--- a/100040000/output.xlsx
+++ b/100040000/output.xlsx
@@ -1,22 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carcheme\PycharmProjects\gyan\mini_project\100040000\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carla\clariant\mini_project\100040000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6ABD958-8CB9-4C0C-8298-BBE217CBD622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84070CBA-3B0E-47AC-AE6D-E318CEC15C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="200122941" sheetId="1" r:id="rId1"/>
     <sheet name="200122942" sheetId="2" r:id="rId2"/>
     <sheet name="200122943" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="bin_200122941">'200122941'!$K$2:INDEX('200122941'!$K:$K,2+COUNT(_xlfn.ANCHORARRAY('200122941'!$K$2))-1)</definedName>
+    <definedName name="bin_200122942">'200122942'!$K$2:INDEX('200122942'!$K:$K,2+COUNT(_xlfn.ANCHORARRAY('200122942'!$K$2))-1)</definedName>
+    <definedName name="bin_200122943">'200122943'!$K$2:INDEX('200122943'!$K:$K,2+COUNT(_xlfn.ANCHORARRAY('200122943'!$K$2))-1)</definedName>
+    <definedName name="frequencies_200122941">'200122941'!$M$2:INDEX('200122941'!$M:$M,2+COUNT(_xlfn.ANCHORARRAY('200122941'!$M$2))-1)</definedName>
+    <definedName name="frequencies_200122942">'200122942'!$M$2:INDEX('200122942'!$M:$M,2+COUNT(_xlfn.ANCHORARRAY('200122942'!$M$2))-1)</definedName>
+    <definedName name="frequencies_200122943">'200122943'!$M$2:INDEX('200122943'!$M:$M,2+COUNT(_xlfn.ANCHORARRAY('200122943'!$M$2))-1)</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -57,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="14">
   <si>
     <t>Particle</t>
   </si>
@@ -97,13 +105,24 @@
   <si>
     <t>data_for_mid_calc</t>
   </si>
+  <si>
+    <t>length</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -119,7 +138,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -127,12 +146,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -148,6 +185,1485 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>PSD graph for 200122941</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>[0]!bin_200122941</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[0]!frequencies_200122941</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2767-40DA-AC4C-08CB294076F9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="0"/>
+        <c:axId val="50010001"/>
+        <c:axId val="50010002"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>[0]!bin_200122941</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[0]!frequencies_200122941</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2767-40DA-AC4C-08CB294076F9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="50010001"/>
+        <c:axId val="50010002"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="50010001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Particle Size (nm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50010002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Frequency</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>PSD graph for 200122942</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>[0]!bin_200122942</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[0]!frequencies_200122942</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E494-45F9-ABA6-322657490EE5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="0"/>
+        <c:axId val="50020001"/>
+        <c:axId val="50020002"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>[0]!bin_200122942</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[0]!frequencies_200122942</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E494-45F9-ABA6-322657490EE5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="50020001"/>
+        <c:axId val="50020002"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="50020001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Particle Size (nm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50020002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50020002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Frequency</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50020001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>PSD graph for 200122943</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>[0]!bin_200122943</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>23</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[0]!frequencies_200122943</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8947-4787-97FF-513343D0F8AE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="0"/>
+        <c:axId val="50030001"/>
+        <c:axId val="50030002"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>[0]!bin_200122943</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>23</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[0]!frequencies_200122943</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8947-4787-97FF-513343D0F8AE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="50030001"/>
+        <c:axId val="50030002"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="50030001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Particle Size (nm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50030002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50030002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Frequency</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50030001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -437,14 +1953,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:R201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
@@ -480,8 +1999,11 @@
       <c r="Q1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -501,34 +2023,38 @@
         <v>2.2323363095577351</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" cm="1">
-        <f t="array" ref="K2:K10">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2,J2)</f>
-        <v>0</v>
+        <f t="array" ref="K2:K17">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2,J2)</f>
+        <v>1</v>
       </c>
       <c r="L2" cm="1">
-        <f t="array" ref="L2:L10">(_xlfn.ANCHORARRAY(Q2)+_xlfn.ANCHORARRAY(K2))/2</f>
-        <v>1</v>
+        <f t="array" ref="L2:L17">(_xlfn.ANCHORARRAY(Q2)+_xlfn.ANCHORARRAY(K2))/2</f>
+        <v>1.5</v>
       </c>
       <c r="M2" cm="1">
-        <f t="array" ref="M2:M10">COUNTIFS(B2:B201, "&gt;="&amp;(_xlfn.ANCHORARRAY(K2)-$J$2), B2:B201, "&lt;"&amp;_xlfn.ANCHORARRAY(K2))</f>
+        <f t="array" ref="M2:M17">COUNTIFS(B2:B201, "&gt;="&amp;(_xlfn.ANCHORARRAY(K2)-$J$2), B2:B201, "&lt;"&amp;_xlfn.ANCHORARRAY(K2))</f>
         <v>0</v>
       </c>
       <c r="O2">
         <f>FLOOR(E2,J2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2">
         <f>CEILING(F2,J2)</f>
         <v>16</v>
       </c>
       <c r="Q2" cm="1">
-        <f t="array" ref="Q2:Q10">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
+        <f t="array" ref="Q2:Q17">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R2" cm="1">
+        <f t="array" ref="R2">ROWS(_xlfn.ANCHORARRAY(K2))</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -539,16 +2065,16 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M3">
         <v>3</v>
       </c>
       <c r="Q3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -556,19 +2082,19 @@
         <v>9.9090000000000007</v>
       </c>
       <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>3.5</v>
+      </c>
+      <c r="M4">
+        <v>35</v>
+      </c>
+      <c r="Q4">
         <v>4</v>
       </c>
-      <c r="L4">
-        <v>5</v>
-      </c>
-      <c r="M4">
-        <v>58</v>
-      </c>
-      <c r="Q4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -576,19 +2102,19 @@
         <v>6.2350000000000003</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="M5">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="Q5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -596,19 +2122,19 @@
         <v>9.5640000000000001</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="M6">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="Q6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -616,19 +2142,19 @@
         <v>9.9770000000000003</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="M7">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="Q7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -636,19 +2162,19 @@
         <v>6.31</v>
       </c>
       <c r="K8">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="Q8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -656,19 +2182,19 @@
         <v>7.84</v>
       </c>
       <c r="K9">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>15</v>
+        <v>8.5</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -676,75 +2202,159 @@
         <v>8.923</v>
       </c>
       <c r="K10">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="M10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
         <v>3.1120000000000001</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>10.5</v>
+      </c>
+      <c r="M11">
+        <v>7</v>
+      </c>
+      <c r="Q11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
         <v>9.234</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K12">
+        <v>11</v>
+      </c>
+      <c r="L12">
+        <v>11.5</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
         <v>6.2240000000000002</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K13">
+        <v>12</v>
+      </c>
+      <c r="L13">
+        <v>12.5</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
+      <c r="Q13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
         <v>8.1180000000000003</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K14">
+        <v>13</v>
+      </c>
+      <c r="L14">
+        <v>13.5</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
         <v>6.4050000000000002</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K15">
+        <v>14</v>
+      </c>
+      <c r="L15">
+        <v>14.5</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
         <v>4.2930000000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K16">
+        <v>15</v>
+      </c>
+      <c r="L16">
+        <v>15.5</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
         <v>2.3199999999999998</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K17">
+        <v>16</v>
+      </c>
+      <c r="L17">
+        <v>16.5</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -752,7 +2362,7 @@
         <v>2.9569999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -760,7 +2370,7 @@
         <v>5.452</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -768,7 +2378,7 @@
         <v>2.9569999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -776,7 +2386,7 @@
         <v>3.3809999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -784,7 +2394,7 @@
         <v>4.5949999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -792,7 +2402,7 @@
         <v>3.3809999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -800,7 +2410,7 @@
         <v>4.2770000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -808,7 +2418,7 @@
         <v>6.7629999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -816,7 +2426,7 @@
         <v>6.891</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -824,7 +2434,7 @@
         <v>5.2119999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -832,7 +2442,7 @@
         <v>5.55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -840,7 +2450,7 @@
         <v>4.7679999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -848,7 +2458,7 @@
         <v>5.5010000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -856,7 +2466,7 @@
         <v>4.782</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2218,19 +3828,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:R201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
@@ -2266,8 +3877,11 @@
       <c r="Q1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2287,18 +3901,18 @@
         <v>3.889935694495676</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" cm="1">
-        <f t="array" ref="K2:K12">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2,J2)</f>
+        <f t="array" ref="K2:K22">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2,J2)</f>
         <v>4</v>
       </c>
       <c r="L2" cm="1">
-        <f t="array" ref="L2:L12">(_xlfn.ANCHORARRAY(Q2)+_xlfn.ANCHORARRAY(K2))/2</f>
-        <v>5</v>
+        <f t="array" ref="L2:L22">(_xlfn.ANCHORARRAY(Q2)+_xlfn.ANCHORARRAY(K2))/2</f>
+        <v>4.5</v>
       </c>
       <c r="M2" cm="1">
-        <f t="array" ref="M2:M12">COUNTIFS(B2:B201, "&gt;="&amp;(_xlfn.ANCHORARRAY(K2)-$J$2), B2:B201, "&lt;"&amp;_xlfn.ANCHORARRAY(K2))</f>
+        <f t="array" ref="M2:M22">COUNTIFS(B2:B201, "&gt;="&amp;(_xlfn.ANCHORARRAY(K2)-$J$2), B2:B201, "&lt;"&amp;_xlfn.ANCHORARRAY(K2))</f>
         <v>0</v>
       </c>
       <c r="O2">
@@ -2310,11 +3924,15 @@
         <v>24</v>
       </c>
       <c r="Q2" cm="1">
-        <f t="array" ref="Q2:Q12">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="array" ref="Q2:Q22">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
+        <v>5</v>
+      </c>
+      <c r="R2" cm="1">
+        <f t="array" ref="R2">ROWS(_xlfn.ANCHORARRAY(K2))</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2322,19 +3940,19 @@
         <v>10.012</v>
       </c>
       <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>5.5</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+      <c r="Q3">
         <v>6</v>
       </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>18</v>
-      </c>
-      <c r="Q3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2342,19 +3960,19 @@
         <v>11.888</v>
       </c>
       <c r="K4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="M4">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="Q4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2362,19 +3980,19 @@
         <v>8.5359999999999996</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="M5">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="Q5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2382,19 +4000,19 @@
         <v>6.5970000000000004</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="M6">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="Q6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2402,19 +4020,19 @@
         <v>14.867000000000001</v>
       </c>
       <c r="K7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>15</v>
+        <v>9.5</v>
       </c>
       <c r="M7">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2422,19 +4040,19 @@
         <v>10.012</v>
       </c>
       <c r="K8">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L8">
+        <v>10.5</v>
+      </c>
+      <c r="M8">
         <v>17</v>
       </c>
-      <c r="M8">
-        <v>21</v>
-      </c>
       <c r="Q8">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2442,19 +4060,19 @@
         <v>8.4209999999999994</v>
       </c>
       <c r="K9">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L9">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2462,19 +4080,19 @@
         <v>16.841000000000001</v>
       </c>
       <c r="K10">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L10">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="M10">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Q10">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2482,19 +4100,19 @@
         <v>13.451000000000001</v>
       </c>
       <c r="K11">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="L11">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Q11">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2502,99 +4120,219 @@
         <v>10.946</v>
       </c>
       <c r="K12">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L12">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="Q12">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
         <v>14.702</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K13">
+        <v>15</v>
+      </c>
+      <c r="L13">
+        <v>15.5</v>
+      </c>
+      <c r="M13">
+        <v>12</v>
+      </c>
+      <c r="Q13">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
         <v>16.681000000000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K14">
+        <v>16</v>
+      </c>
+      <c r="L14">
+        <v>16.5</v>
+      </c>
+      <c r="M14">
+        <v>9</v>
+      </c>
+      <c r="Q14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
         <v>10.012</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K15">
+        <v>17</v>
+      </c>
+      <c r="L15">
+        <v>17.5</v>
+      </c>
+      <c r="M15">
+        <v>6</v>
+      </c>
+      <c r="Q15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
         <v>5.6379999999999999</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K16">
+        <v>18</v>
+      </c>
+      <c r="L16">
+        <v>18.5</v>
+      </c>
+      <c r="M16">
+        <v>4</v>
+      </c>
+      <c r="Q16">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
         <v>8.4499999999999993</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K17">
+        <v>19</v>
+      </c>
+      <c r="L17">
+        <v>19.5</v>
+      </c>
+      <c r="M17">
+        <v>2</v>
+      </c>
+      <c r="Q17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
         <v>9.8149999999999995</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K18">
+        <v>20</v>
+      </c>
+      <c r="L18">
+        <v>20.5</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
         <v>7.4340000000000002</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K19">
+        <v>21</v>
+      </c>
+      <c r="L19">
+        <v>21.5</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
         <v>8.1549999999999994</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K20">
+        <v>22</v>
+      </c>
+      <c r="L20">
+        <v>22.5</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
         <v>11.057</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K21">
+        <v>23</v>
+      </c>
+      <c r="L21">
+        <v>23.5</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="Q21">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
         <v>8.5069999999999997</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K22">
+        <v>24</v>
+      </c>
+      <c r="L22">
+        <v>24.5</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2602,7 +4340,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2610,7 +4348,7 @@
         <v>14.16</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2618,7 +4356,7 @@
         <v>11.276</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2626,7 +4364,7 @@
         <v>12.606999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2634,7 +4372,7 @@
         <v>13.933</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2642,7 +4380,7 @@
         <v>14.818</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2650,7 +4388,7 @@
         <v>12.606999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2658,7 +4396,7 @@
         <v>8.4209999999999994</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2666,7 +4404,7 @@
         <v>12.451000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4028,19 +5766,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:R201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
@@ -4076,8 +5815,11 @@
       <c r="Q1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4097,18 +5839,18 @@
         <v>2.9333624933833078</v>
       </c>
       <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2" cm="1">
+        <f t="array" ref="K2:K23">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2,J2)</f>
         <v>2</v>
       </c>
-      <c r="K2" cm="1">
-        <f t="array" ref="K2:K13">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2,J2)</f>
-        <v>2</v>
-      </c>
       <c r="L2" cm="1">
-        <f t="array" ref="L2:L13">(_xlfn.ANCHORARRAY(Q2)+_xlfn.ANCHORARRAY(K2))/2</f>
-        <v>3</v>
+        <f t="array" ref="L2:L23">(_xlfn.ANCHORARRAY(Q2)+_xlfn.ANCHORARRAY(K2))/2</f>
+        <v>2.5</v>
       </c>
       <c r="M2" cm="1">
-        <f t="array" ref="M2:M13">COUNTIFS(B2:B201, "&gt;="&amp;(_xlfn.ANCHORARRAY(K2)-$J$2), B2:B201, "&lt;"&amp;_xlfn.ANCHORARRAY(K2))</f>
+        <f t="array" ref="M2:M23">COUNTIFS(B2:B201, "&gt;="&amp;(_xlfn.ANCHORARRAY(K2)-$J$2), B2:B201, "&lt;"&amp;_xlfn.ANCHORARRAY(K2))</f>
         <v>0</v>
       </c>
       <c r="O2">
@@ -4117,14 +5859,18 @@
       </c>
       <c r="P2">
         <f>CEILING(F2,J2)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q2" cm="1">
-        <f t="array" ref="Q2:Q13">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="array" ref="Q2:Q23">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
+        <v>3</v>
+      </c>
+      <c r="R2" cm="1">
+        <f t="array" ref="R2">ROWS(_xlfn.ANCHORARRAY(K2))</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4132,19 +5878,19 @@
         <v>16.247</v>
       </c>
       <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>3.5</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+      <c r="Q3">
         <v>4</v>
       </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>12</v>
-      </c>
-      <c r="Q3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4152,19 +5898,19 @@
         <v>4.4059999999999997</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L4">
+        <v>4.5</v>
+      </c>
+      <c r="M4">
         <v>7</v>
       </c>
-      <c r="M4">
-        <v>41</v>
-      </c>
       <c r="Q4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4172,19 +5918,19 @@
         <v>4.4809999999999999</v>
       </c>
       <c r="K5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="M5">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="Q5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4192,19 +5938,19 @@
         <v>3.1859999999999999</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="M6">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="Q6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4212,19 +5958,19 @@
         <v>3.3239999999999998</v>
       </c>
       <c r="K7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="M7">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4232,19 +5978,19 @@
         <v>5.633</v>
       </c>
       <c r="K8">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>15</v>
+        <v>8.5</v>
       </c>
       <c r="M8">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="Q8">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4252,19 +5998,19 @@
         <v>7.4020000000000001</v>
       </c>
       <c r="K9">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Q9">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4272,19 +6018,19 @@
         <v>9.0210000000000008</v>
       </c>
       <c r="K10">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="M10">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Q10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4292,19 +6038,19 @@
         <v>4.8869999999999996</v>
       </c>
       <c r="K11">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="L11">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q11">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4312,19 +6058,19 @@
         <v>5.31</v>
       </c>
       <c r="K12">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="L12">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4332,99 +6078,219 @@
         <v>7.1989999999999998</v>
       </c>
       <c r="K13">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="L13">
-        <v>25</v>
+        <v>13.5</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
         <v>6.8940000000000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K14">
+        <v>14</v>
+      </c>
+      <c r="L14">
+        <v>14.5</v>
+      </c>
+      <c r="M14">
+        <v>5</v>
+      </c>
+      <c r="Q14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
         <v>5.2629999999999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K15">
+        <v>15</v>
+      </c>
+      <c r="L15">
+        <v>15.5</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
         <v>5.9649999999999999</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K16">
+        <v>16</v>
+      </c>
+      <c r="L16">
+        <v>16.5</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="Q16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
         <v>5.9649999999999999</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K17">
+        <v>17</v>
+      </c>
+      <c r="L17">
+        <v>17.5</v>
+      </c>
+      <c r="M17">
+        <v>2</v>
+      </c>
+      <c r="Q17">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
         <v>8.4870000000000001</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K18">
+        <v>18</v>
+      </c>
+      <c r="L18">
+        <v>18.5</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
         <v>5.9749999999999996</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K19">
+        <v>19</v>
+      </c>
+      <c r="L19">
+        <v>19.5</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
         <v>7.1050000000000004</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K20">
+        <v>20</v>
+      </c>
+      <c r="L20">
+        <v>20.5</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
         <v>7.0259999999999998</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K21">
+        <v>21</v>
+      </c>
+      <c r="L21">
+        <v>21.5</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
         <v>7.157</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K22">
+        <v>22</v>
+      </c>
+      <c r="L22">
+        <v>22.5</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
         <v>7.7670000000000003</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K23">
+        <v>23</v>
+      </c>
+      <c r="L23">
+        <v>23.5</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4432,7 +6298,7 @@
         <v>2.2469999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4440,7 +6306,7 @@
         <v>5.109</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4448,7 +6314,7 @@
         <v>11.664</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4456,7 +6322,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4464,7 +6330,7 @@
         <v>8.1389999999999993</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4472,7 +6338,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4480,7 +6346,7 @@
         <v>5.6580000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4488,7 +6354,7 @@
         <v>6.9109999999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5850,5 +7716,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/100040000/output.xlsx
+++ b/100040000/output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carla\clariant\mini_project\100040000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84070CBA-3B0E-47AC-AE6D-E318CEC15C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02C0C0D-2FF9-4932-A041-89FB8E8D76E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="23985" windowHeight="13650" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="200122941" sheetId="1" r:id="rId1"/>
@@ -65,12 +65,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="13">
   <si>
-    <t>Particle</t>
+    <t>Particle (N)</t>
   </si>
   <si>
-    <t>Diameter (nm)</t>
+    <t>Particle Size (nm)</t>
   </si>
   <si>
     <t>min</t>
@@ -104,9 +104,6 @@
   </si>
   <si>
     <t>data_for_mid_calc</t>
-  </si>
-  <si>
-    <t>length</t>
   </si>
 </sst>
 </file>
@@ -346,7 +343,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2767-40DA-AC4C-08CB294076F9}"/>
+              <c16:uniqueId val="{00000000-55F2-4417-BED0-5DEC22F04B37}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -495,7 +492,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2767-40DA-AC4C-08CB294076F9}"/>
+              <c16:uniqueId val="{00000001-55F2-4417-BED0-5DEC22F04B37}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -784,7 +781,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E494-45F9-ABA6-322657490EE5}"/>
+              <c16:uniqueId val="{00000000-B843-4813-A27F-917E720B351A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -963,7 +960,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E494-45F9-ABA6-322657490EE5}"/>
+              <c16:uniqueId val="{00000001-B843-4813-A27F-917E720B351A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1258,7 +1255,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8947-4787-97FF-513343D0F8AE}"/>
+              <c16:uniqueId val="{00000000-5AC7-42E9-B465-F57434AC6520}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1443,7 +1440,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8947-4787-97FF-513343D0F8AE}"/>
+              <c16:uniqueId val="{00000001-5AC7-42E9-B465-F57434AC6520}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1548,15 +1545,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1588,15 +1585,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1629,16 +1626,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1953,13 +1950,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R201"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1999,11 +1997,8 @@
       <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2049,12 +2044,8 @@
         <f t="array" ref="Q2:Q17">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
         <v>2</v>
       </c>
-      <c r="R2" cm="1">
-        <f t="array" ref="R2">ROWS(_xlfn.ANCHORARRAY(K2))</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2074,7 +2065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2094,7 +2085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2114,7 +2105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2134,7 +2125,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2154,7 +2145,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2174,7 +2165,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2194,7 +2185,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2214,7 +2205,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2234,7 +2225,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2254,7 +2245,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2274,7 +2265,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2294,7 +2285,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2314,7 +2305,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3834,10 +3825,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R201"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3877,11 +3872,8 @@
       <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3927,12 +3919,8 @@
         <f t="array" ref="Q2:Q22">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
         <v>5</v>
       </c>
-      <c r="R2" cm="1">
-        <f t="array" ref="R2">ROWS(_xlfn.ANCHORARRAY(K2))</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3952,7 +3940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3972,7 +3960,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3992,7 +3980,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4012,7 +4000,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4032,7 +4020,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4052,7 +4040,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4072,7 +4060,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4092,7 +4080,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4112,7 +4100,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4132,7 +4120,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4152,7 +4140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4172,7 +4160,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4192,7 +4180,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5772,10 +5760,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R201"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5815,11 +5808,8 @@
       <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5865,12 +5855,8 @@
         <f t="array" ref="Q2:Q23">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
         <v>3</v>
       </c>
-      <c r="R2" cm="1">
-        <f t="array" ref="R2">ROWS(_xlfn.ANCHORARRAY(K2))</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5890,7 +5876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5910,7 +5896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5930,7 +5916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5950,7 +5936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5970,7 +5956,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5990,7 +5976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6010,7 +5996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -6030,7 +6016,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6050,7 +6036,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6070,7 +6056,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6090,7 +6076,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6110,7 +6096,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6130,7 +6116,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>

--- a/100040000/output.xlsx
+++ b/100040000/output.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carla\clariant\mini_project\100040000\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02C0C0D-2FF9-4932-A041-89FB8E8D76E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="23985" windowHeight="13650" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="200122941" sheetId="1" r:id="rId1"/>
@@ -18,27 +12,14 @@
     <sheet name="200122943" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="bin_200122941">'200122941'!$K$2:INDEX('200122941'!$K:$K,2+COUNT(_xlfn.ANCHORARRAY('200122941'!$K$2))-1)</definedName>
-    <definedName name="bin_200122942">'200122942'!$K$2:INDEX('200122942'!$K:$K,2+COUNT(_xlfn.ANCHORARRAY('200122942'!$K$2))-1)</definedName>
-    <definedName name="bin_200122943">'200122943'!$K$2:INDEX('200122943'!$K:$K,2+COUNT(_xlfn.ANCHORARRAY('200122943'!$K$2))-1)</definedName>
-    <definedName name="frequencies_200122941">'200122941'!$M$2:INDEX('200122941'!$M:$M,2+COUNT(_xlfn.ANCHORARRAY('200122941'!$M$2))-1)</definedName>
-    <definedName name="frequencies_200122942">'200122942'!$M$2:INDEX('200122942'!$M:$M,2+COUNT(_xlfn.ANCHORARRAY('200122942'!$M$2))-1)</definedName>
-    <definedName name="frequencies_200122943">'200122943'!$M$2:INDEX('200122943'!$M:$M,2+COUNT(_xlfn.ANCHORARRAY('200122943'!$M$2))-1)</definedName>
+    <definedName name="bin_200122941">200122941!$K$2:INDEX(200122941!$K:$K,2+COUNT(_xlfn.ANCHORARRAY(200122941!$K$2))-1)</definedName>
+    <definedName name="bin_200122942">200122942!$K$2:INDEX(200122942!$K:$K,2+COUNT(_xlfn.ANCHORARRAY(200122942!$K$2))-1)</definedName>
+    <definedName name="bin_200122943">200122943!$K$2:INDEX(200122943!$K:$K,2+COUNT(_xlfn.ANCHORARRAY(200122943!$K$2))-1)</definedName>
+    <definedName name="frequencies_200122941">200122941!$M$2:INDEX(200122941!$M:$M,2+COUNT(_xlfn.ANCHORARRAY(200122941!$M$2))-1)</definedName>
+    <definedName name="frequencies_200122942">200122942!$M$2:INDEX(200122942!$M:$M,2+COUNT(_xlfn.ANCHORARRAY(200122942!$M$2))-1)</definedName>
+    <definedName name="frequencies_200122943">200122943!$M$2:INDEX(200122943!$M:$M,2+COUNT(_xlfn.ANCHORARRAY(200122943!$M$2))-1)</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -65,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="13">
   <si>
     <t>Particle (N)</t>
   </si>
@@ -109,8 +90,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,6 +103,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -144,15 +132,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -162,41 +144,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -214,154 +183,46 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>[0]!bin_200122941</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+            <c:strRef>
+              <c:f>200122941!bin_200122941</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>Particle (N)</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>[0]!frequencies_200122941</c:f>
+              <c:f>200122941!frequencies_200122941</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>34</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-55F2-4417-BED0-5DEC22F04B37}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:gapWidth val="0"/>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -376,136 +237,31 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:numRef>
-              <c:f>[0]!bin_200122941</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+            <c:strRef>
+              <c:f>200122941!bin_200122941</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>Particle (N)</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>[0]!frequencies_200122941</c:f>
+              <c:f>200122941!frequencies_200122941</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>34</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-55F2-4417-BED0-5DEC22F04B37}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:marker val="1"/>
-        <c:smooth val="0"/>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
       </c:lineChart>
@@ -514,7 +270,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -532,18 +287,15 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50010002"/>
@@ -551,7 +303,6 @@
           <c:orientation val="minMax"/>
           <c:min val="0"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:title>
           <c:tx>
@@ -569,11 +320,10 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010001"/>
         <c:crosses val="autoZero"/>
@@ -581,8 +331,6 @@
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -593,18 +341,8 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -622,184 +360,46 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>[0]!bin_200122942</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+            <c:strRef>
+              <c:f>200122942!bin_200122942</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>Particle (N)</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>24</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>[0]!frequencies_200122942</c:f>
+              <c:f>200122942!frequencies_200122942</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B843-4813-A27F-917E720B351A}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:gapWidth val="0"/>
         <c:axId val="50020001"/>
         <c:axId val="50020002"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -814,166 +414,31 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:numRef>
-              <c:f>[0]!bin_200122942</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+            <c:strRef>
+              <c:f>200122942!bin_200122942</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>Particle (N)</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>24</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>[0]!frequencies_200122942</c:f>
+              <c:f>200122942!frequencies_200122942</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-B843-4813-A27F-917E720B351A}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:marker val="1"/>
-        <c:smooth val="0"/>
         <c:axId val="50020001"/>
         <c:axId val="50020002"/>
       </c:lineChart>
@@ -982,7 +447,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -1000,18 +464,15 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50020002"/>
@@ -1019,7 +480,6 @@
           <c:orientation val="minMax"/>
           <c:min val="0"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:title>
           <c:tx>
@@ -1037,11 +497,10 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
@@ -1049,8 +508,6 @@
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1061,18 +518,8 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1090,190 +537,46 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>[0]!bin_200122943</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+            <c:strRef>
+              <c:f>200122943!bin_200122943</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>Particle (N)</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>23</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>[0]!frequencies_200122943</c:f>
+              <c:f>200122943!frequencies_200122943</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5AC7-42E9-B465-F57434AC6520}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:gapWidth val="0"/>
         <c:axId val="50030001"/>
         <c:axId val="50030002"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -1288,172 +591,31 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:numRef>
-              <c:f>[0]!bin_200122943</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+            <c:strRef>
+              <c:f>200122943!bin_200122943</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>Particle (N)</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>23</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>[0]!frequencies_200122943</c:f>
+              <c:f>200122943!frequencies_200122943</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5AC7-42E9-B465-F57434AC6520}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:marker val="1"/>
-        <c:smooth val="0"/>
         <c:axId val="50030001"/>
         <c:axId val="50030002"/>
       </c:lineChart>
@@ -1462,7 +624,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -1480,18 +641,15 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50030002"/>
@@ -1499,7 +657,6 @@
           <c:orientation val="minMax"/>
           <c:min val="0"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:title>
           <c:tx>
@@ -1517,11 +674,10 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030001"/>
         <c:crosses val="autoZero"/>
@@ -1529,8 +685,6 @@
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1557,13 +711,7 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1598,13 +746,7 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1639,13 +781,7 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1664,9 +800,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1704,7 +840,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1738,7 +874,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1773,10 +908,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1949,15 +1083,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q201"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1988,372 +1122,192 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="Q1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6.6929999999999996</v>
+        <v>6.693</v>
       </c>
       <c r="E2">
         <v>1.78</v>
       </c>
       <c r="F2">
-        <v>15.202999999999999</v>
+        <v>15.203</v>
       </c>
       <c r="G2">
-        <v>5.2943049999999996</v>
+        <v>5.294305</v>
       </c>
       <c r="H2">
-        <v>2.2323363095577351</v>
+        <v>2.232336309557735</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" cm="1">
-        <f t="array" ref="K2:K17">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2,J2)</f>
-        <v>1</v>
+        <f t="array" ref="K2">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2,J2)</f>
+        <v>0</v>
       </c>
       <c r="L2" cm="1">
-        <f t="array" ref="L2:L17">(_xlfn.ANCHORARRAY(Q2)+_xlfn.ANCHORARRAY(K2))/2</f>
-        <v>1.5</v>
+        <f t="array" ref="L2">(_xlfn.ANCHORARRAY(Q2)+_xlfn.ANCHORARRAY(K2))/2</f>
+        <v>0</v>
       </c>
       <c r="M2" cm="1">
-        <f t="array" ref="M2:M17">COUNTIFS(B2:B201, "&gt;="&amp;(_xlfn.ANCHORARRAY(K2)-$J$2), B2:B201, "&lt;"&amp;_xlfn.ANCHORARRAY(K2))</f>
+        <f t="array" ref="M2">COUNTIFS(B2:B201, "&gt;="&amp;(_xlfn.ANCHORARRAY(K2)-$J$2), B2:B201, "&lt;"&amp;_xlfn.ANCHORARRAY(K2))</f>
         <v>0</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="2">
         <f>FLOOR(E2,J2)</f>
-        <v>1</v>
-      </c>
-      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
         <f>CEILING(F2,J2)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q2" cm="1">
-        <f t="array" ref="Q2:Q17">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="array" ref="Q2">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4.5359999999999996</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2.5</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-      <c r="Q3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+        <v>4.536</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>9.9090000000000007</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>3.5</v>
-      </c>
-      <c r="M4">
-        <v>35</v>
-      </c>
-      <c r="Q4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <v>9.909000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>6.2350000000000003</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>4.5</v>
-      </c>
-      <c r="M5">
-        <v>23</v>
-      </c>
-      <c r="Q5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>6.235</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9.5640000000000001</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>5.5</v>
-      </c>
-      <c r="M6">
-        <v>36</v>
-      </c>
-      <c r="Q6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <v>9.564</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>9.9770000000000003</v>
-      </c>
-      <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>6.5</v>
-      </c>
-      <c r="M7">
-        <v>34</v>
-      </c>
-      <c r="Q7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <v>9.977</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>6.31</v>
       </c>
-      <c r="K8">
-        <v>7</v>
-      </c>
-      <c r="L8">
-        <v>7.5</v>
-      </c>
-      <c r="M8">
-        <v>35</v>
-      </c>
-      <c r="Q8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
         <v>7.84</v>
       </c>
-      <c r="K9">
-        <v>8</v>
-      </c>
-      <c r="L9">
-        <v>8.5</v>
-      </c>
-      <c r="M9">
-        <v>12</v>
-      </c>
-      <c r="Q9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
         <v>8.923</v>
       </c>
-      <c r="K10">
-        <v>9</v>
-      </c>
-      <c r="L10">
-        <v>9.5</v>
-      </c>
-      <c r="M10">
-        <v>10</v>
-      </c>
-      <c r="Q10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>3.1120000000000001</v>
-      </c>
-      <c r="K11">
-        <v>10</v>
-      </c>
-      <c r="L11">
-        <v>10.5</v>
-      </c>
-      <c r="M11">
-        <v>7</v>
-      </c>
-      <c r="Q11">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>3.112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
         <v>9.234</v>
       </c>
-      <c r="K12">
-        <v>11</v>
-      </c>
-      <c r="L12">
-        <v>11.5</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="Q12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>6.2240000000000002</v>
-      </c>
-      <c r="K13">
-        <v>12</v>
-      </c>
-      <c r="L13">
-        <v>12.5</v>
-      </c>
-      <c r="M13">
-        <v>2</v>
-      </c>
-      <c r="Q13">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <v>6.224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>8.1180000000000003</v>
-      </c>
-      <c r="K14">
-        <v>13</v>
-      </c>
-      <c r="L14">
-        <v>13.5</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="Q14">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+        <v>8.118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>6.4050000000000002</v>
-      </c>
-      <c r="K15">
-        <v>14</v>
-      </c>
-      <c r="L15">
-        <v>14.5</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+        <v>6.405</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>4.2930000000000001</v>
-      </c>
-      <c r="K16">
-        <v>15</v>
-      </c>
-      <c r="L16">
-        <v>15.5</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <v>4.293</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="K17">
-        <v>16</v>
-      </c>
-      <c r="L17">
-        <v>16.5</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="Q17">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>2.9569999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <v>2.957</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2361,55 +1315,55 @@
         <v>5.452</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>2.9569999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+        <v>2.957</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>3.3809999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+        <v>3.381</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>4.5949999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+        <v>4.595</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>3.3809999999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+        <v>3.381</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>4.2770000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+        <v>4.277</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>6.7629999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+        <v>6.763</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2417,15 +1371,15 @@
         <v>6.891</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>5.2119999999999997</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5.212</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2433,23 +1387,23 @@
         <v>5.55</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29">
-        <v>4.7679999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+        <v>4.768</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30">
-        <v>5.5010000000000003</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5.501</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2457,7 +1411,7 @@
         <v>4.782</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2465,79 +1419,79 @@
         <v>5.452</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33">
-        <v>9.8409999999999993</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.840999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34">
-        <v>4.5949999999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.595</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35">
-        <v>6.7629999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.763</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36">
-        <v>5.2889999999999997</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.289</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37">
-        <v>5.8680000000000003</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.868</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38">
-        <v>3.3809999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.381</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39">
-        <v>4.0339999999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.034</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40">
-        <v>5.7990000000000004</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.799</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41">
-        <v>5.5010000000000003</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.501</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2545,7 +1499,7 @@
         <v>7.78</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2553,55 +1507,55 @@
         <v>4.149</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44">
-        <v>4.2770000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.277</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45">
-        <v>5.7990000000000004</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.799</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46">
-        <v>6.2779999999999996</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.278</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47">
-        <v>4.2770000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.277</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48">
-        <v>2.9340000000000002</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.934</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49">
-        <v>8.8629999999999995</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.863</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2609,63 +1563,63 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51">
-        <v>4.6970000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.697</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52">
-        <v>5.5979999999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.598</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53">
-        <v>2.0750000000000002</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.075</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54">
-        <v>5.2510000000000003</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.251</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55">
-        <v>6.0709999999999997</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.071</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56">
-        <v>6.6120000000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.612</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57">
-        <v>9.6389999999999993</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.638999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2673,55 +1627,55 @@
         <v>6.53</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59">
-        <v>9.1690000000000005</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.169</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60">
-        <v>4.6680000000000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.668</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61">
-        <v>6.7629999999999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.763</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62">
-        <v>5.7290000000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.729</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63">
-        <v>6.7629999999999999</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.763</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64">
-        <v>7.0549999999999997</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.055</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2729,47 +1683,47 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66">
-        <v>4.4619999999999997</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.462</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67">
-        <v>6.5609999999999999</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.561</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68">
-        <v>5.5860000000000003</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.586</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69">
-        <v>5.7050000000000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.705</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70">
-        <v>4.6390000000000002</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.639</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2777,15 +1731,15 @@
         <v>4.782</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72">
-        <v>5.1079999999999997</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.108</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2793,31 +1747,31 @@
         <v>4.431</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74">
-        <v>7.2610000000000001</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.261</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75">
-        <v>7.3440000000000003</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.344</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76">
-        <v>4.1820000000000004</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.182</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2825,23 +1779,23 @@
         <v>4.782</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78">
-        <v>6.6420000000000003</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.642</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79">
-        <v>5.1870000000000003</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.187</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2849,47 +1803,47 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81">
-        <v>6.2779999999999996</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.278</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82">
-        <v>3.9529999999999998</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.953</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83">
-        <v>5.4260000000000002</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.426</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84">
-        <v>6.7809999999999997</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.781</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85">
-        <v>6.5279999999999996</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.528</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2897,7 +1851,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2905,15 +1859,15 @@
         <v>7.37</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88">
-        <v>5.5510000000000002</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.551</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2921,7 +1875,7 @@
         <v>2.109</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2929,63 +1883,63 @@
         <v>3.105</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91">
-        <v>2.7429999999999999</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.743</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92">
-        <v>3.1349999999999998</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.135</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93">
-        <v>7.4930000000000003</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.493</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94">
-        <v>6.0469999999999997</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.047</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95">
-        <v>5.9660000000000002</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.966</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96">
-        <v>4.8289999999999997</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.829</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97">
-        <v>6.4189999999999996</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.419</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -2993,15 +1947,15 @@
         <v>2.859</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99">
-        <v>4.7229999999999999</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.723</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3009,7 +1963,7 @@
         <v>10.398</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3017,47 +1971,47 @@
         <v>3.569</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102">
-        <v>2.9249999999999998</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.925</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
       <c r="A103">
         <v>102</v>
       </c>
       <c r="B103">
-        <v>2.6360000000000001</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.636</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104">
-        <v>4.1859999999999999</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.186</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105">
-        <v>2.8959999999999999</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.896</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106">
-        <v>4.1980000000000004</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.198</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -3065,79 +2019,79 @@
         <v>5.72</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108">
-        <v>6.3109999999999999</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.311</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
       <c r="A109">
         <v>108</v>
       </c>
       <c r="B109">
-        <v>8.0640000000000001</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.064</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110">
-        <v>5.6429999999999998</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.643</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111">
-        <v>8.1920000000000002</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.192</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
       <c r="A112">
         <v>111</v>
       </c>
       <c r="B112">
-        <v>2.2360000000000002</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.236</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113">
-        <v>4.8159999999999998</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.816</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114">
-        <v>5.7889999999999997</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.789</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115">
-        <v>8.5990000000000002</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.599</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116">
-        <v>7.4050000000000002</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.405</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
       <c r="A117">
         <v>116</v>
       </c>
@@ -3145,31 +2099,31 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118">
-        <v>3.2959999999999998</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.296</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
       <c r="A119">
         <v>118</v>
       </c>
       <c r="B119">
-        <v>5.8940000000000001</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.894</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120">
-        <v>6.9420000000000002</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.942</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
       <c r="A121">
         <v>120</v>
       </c>
@@ -3177,15 +2131,15 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2">
       <c r="A122">
         <v>121</v>
       </c>
       <c r="B122">
-        <v>2.4809999999999999</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.481</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
       <c r="A123">
         <v>122</v>
       </c>
@@ -3193,55 +2147,55 @@
         <v>3.879</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2">
       <c r="A124">
         <v>123</v>
       </c>
       <c r="B124">
-        <v>5.8440000000000003</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.844</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
       <c r="A125">
         <v>124</v>
       </c>
       <c r="B125">
-        <v>2.1539999999999999</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.154</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126">
-        <v>3.9039999999999999</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.904</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
       <c r="A127">
         <v>126</v>
       </c>
       <c r="B127">
-        <v>8.0500000000000007</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.050000000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
       <c r="A128">
         <v>127</v>
       </c>
       <c r="B128">
-        <v>11.183999999999999</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11.184</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
       <c r="A129">
         <v>128</v>
       </c>
       <c r="B129">
-        <v>2.7120000000000002</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.712</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
       <c r="A130">
         <v>129</v>
       </c>
@@ -3249,39 +2203,39 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2">
       <c r="A131">
         <v>130</v>
       </c>
       <c r="B131">
-        <v>5.9640000000000004</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.964</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
       <c r="A132">
         <v>131</v>
       </c>
       <c r="B132">
-        <v>2.9129999999999998</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.913</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
       <c r="A133">
         <v>132</v>
       </c>
       <c r="B133">
-        <v>4.6020000000000003</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.602</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
       <c r="A134">
         <v>133</v>
       </c>
       <c r="B134">
-        <v>5.4290000000000003</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.429</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
       <c r="A135">
         <v>134</v>
       </c>
@@ -3289,71 +2243,71 @@
         <v>12.757</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2">
       <c r="A136">
         <v>135</v>
       </c>
       <c r="B136">
-        <v>4.0250000000000004</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.025</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
       <c r="A137">
         <v>136</v>
       </c>
       <c r="B137">
-        <v>5.6879999999999997</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.688</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
       <c r="A138">
         <v>137</v>
       </c>
       <c r="B138">
-        <v>7.4050000000000002</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.405</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
       <c r="A139">
         <v>138</v>
       </c>
       <c r="B139">
-        <v>6.5780000000000003</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.578</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
       <c r="A140">
         <v>139</v>
       </c>
       <c r="B140">
-        <v>4.1050000000000004</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.105</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
       <c r="A141">
         <v>140</v>
       </c>
       <c r="B141">
-        <v>15.202999999999999</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15.203</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
       <c r="A142">
         <v>141</v>
       </c>
       <c r="B142">
-        <v>4.3259999999999996</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.326</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
       <c r="A143">
         <v>142</v>
       </c>
       <c r="B143">
-        <v>2.2309999999999999</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.231</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
       <c r="A144">
         <v>143</v>
       </c>
@@ -3361,55 +2315,55 @@
         <v>2.714</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2">
       <c r="A145">
         <v>144</v>
       </c>
       <c r="B145">
-        <v>4.5359999999999996</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.536</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
       <c r="A146">
         <v>145</v>
       </c>
       <c r="B146">
-        <v>4.0490000000000004</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.049</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
       <c r="A147">
         <v>146</v>
       </c>
       <c r="B147">
-        <v>3.5640000000000001</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.564</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
       <c r="A148">
         <v>147</v>
       </c>
       <c r="B148">
-        <v>7.0380000000000003</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.038</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
       <c r="A149">
         <v>148</v>
       </c>
       <c r="B149">
-        <v>5.5229999999999997</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.523</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
       <c r="A150">
         <v>149</v>
       </c>
       <c r="B150">
-        <v>2.8540000000000001</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.854</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
       <c r="A151">
         <v>150</v>
       </c>
@@ -3417,39 +2371,39 @@
         <v>3.798</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2">
       <c r="A152">
         <v>151</v>
       </c>
       <c r="B152">
-        <v>6.3109999999999999</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.311</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
       <c r="A153">
         <v>152</v>
       </c>
       <c r="B153">
-        <v>6.2110000000000003</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.211</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
       <c r="A154">
         <v>153</v>
       </c>
       <c r="B154">
-        <v>2.4569999999999999</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.457</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
       <c r="A155">
         <v>154</v>
       </c>
       <c r="B155">
-        <v>1.9710000000000001</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.971</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
       <c r="A156">
         <v>155</v>
       </c>
@@ -3457,15 +2411,15 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2">
       <c r="A157">
         <v>156</v>
       </c>
       <c r="B157">
-        <v>3.9119999999999999</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.912</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
       <c r="A158">
         <v>157</v>
       </c>
@@ -3473,31 +2427,31 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2">
       <c r="A159">
         <v>158</v>
       </c>
       <c r="B159">
-        <v>5.4009999999999998</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.401</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
       <c r="A160">
         <v>159</v>
       </c>
       <c r="B160">
-        <v>2.1349999999999998</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.135</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
       <c r="A161">
         <v>160</v>
       </c>
       <c r="B161">
-        <v>8.4410000000000007</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.441000000000001</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
       <c r="A162">
         <v>161</v>
       </c>
@@ -3505,47 +2459,47 @@
         <v>6.524</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2">
       <c r="A163">
         <v>162</v>
       </c>
       <c r="B163">
-        <v>4.3410000000000002</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.341</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
       <c r="A164">
         <v>163</v>
       </c>
       <c r="B164">
-        <v>4.4160000000000004</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.416</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
       <c r="A165">
         <v>164</v>
       </c>
       <c r="B165">
-        <v>4.8440000000000003</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.844</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
       <c r="A166">
         <v>165</v>
       </c>
       <c r="B166">
-        <v>2.8119999999999998</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.812</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
       <c r="A167">
         <v>166</v>
       </c>
       <c r="B167">
-        <v>2.1349999999999998</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.135</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
       <c r="A168">
         <v>167</v>
       </c>
@@ -3553,23 +2507,23 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2">
       <c r="A169">
         <v>168</v>
       </c>
       <c r="B169">
-        <v>5.4939999999999998</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.494</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
       <c r="A170">
         <v>169</v>
       </c>
       <c r="B170">
-        <v>6.8159999999999998</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.816</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
       <c r="A171">
         <v>170</v>
       </c>
@@ -3577,7 +2531,7 @@
         <v>2.472</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2">
       <c r="A172">
         <v>171</v>
       </c>
@@ -3585,7 +2539,7 @@
         <v>2.714</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2">
       <c r="A173">
         <v>172</v>
       </c>
@@ -3593,7 +2547,7 @@
         <v>3.839</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2">
       <c r="A174">
         <v>173</v>
       </c>
@@ -3601,23 +2555,23 @@
         <v>6.915</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2">
       <c r="A175">
         <v>174</v>
       </c>
       <c r="B175">
-        <v>3.0779999999999998</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.078</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
       <c r="A176">
         <v>175</v>
       </c>
       <c r="B176">
-        <v>3.3570000000000002</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.357</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
       <c r="A177">
         <v>176</v>
       </c>
@@ -3625,31 +2579,31 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2">
       <c r="A178">
         <v>177</v>
       </c>
       <c r="B178">
-        <v>3.5259999999999998</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.526</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
       <c r="A179">
         <v>178</v>
       </c>
       <c r="B179">
-        <v>2.9740000000000002</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.974</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
       <c r="A180">
         <v>179</v>
       </c>
       <c r="B180">
-        <v>2.3740000000000001</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.374</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
       <c r="A181">
         <v>180</v>
       </c>
@@ -3657,31 +2611,31 @@
         <v>2.851</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2">
       <c r="A182">
         <v>181</v>
       </c>
       <c r="B182">
-        <v>3.5259999999999998</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.526</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
       <c r="A183">
         <v>182</v>
       </c>
       <c r="B183">
-        <v>4.5229999999999997</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.523</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
       <c r="A184">
         <v>183</v>
       </c>
       <c r="B184">
-        <v>7.4640000000000004</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.464</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
       <c r="A185">
         <v>184</v>
       </c>
@@ -3689,31 +2643,31 @@
         <v>2.411</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2">
       <c r="A186">
         <v>185</v>
       </c>
       <c r="B186">
-        <v>3.6349999999999998</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.635</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
       <c r="A187">
         <v>186</v>
       </c>
       <c r="B187">
-        <v>2.7719999999999998</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.772</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
       <c r="A188">
         <v>187</v>
       </c>
       <c r="B188">
-        <v>8.4209999999999994</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.420999999999999</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
       <c r="A189">
         <v>188</v>
       </c>
@@ -3721,39 +2675,39 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2">
       <c r="A190">
         <v>189</v>
       </c>
       <c r="B190">
-        <v>8.6509999999999998</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.651</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
       <c r="A191">
         <v>190</v>
       </c>
       <c r="B191">
-        <v>6.1139999999999999</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.114</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
       <c r="A192">
         <v>191</v>
       </c>
       <c r="B192">
-        <v>6.5720000000000001</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.572</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
       <c r="A193">
         <v>192</v>
       </c>
       <c r="B193">
-        <v>1.8380000000000001</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.838</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
       <c r="A194">
         <v>193</v>
       </c>
@@ -3761,15 +2715,15 @@
         <v>11.388</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2">
       <c r="A195">
         <v>194</v>
       </c>
       <c r="B195">
-        <v>6.9539999999999997</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.954</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
       <c r="A196">
         <v>195</v>
       </c>
@@ -3777,7 +2731,7 @@
         <v>6.915</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2">
       <c r="A197">
         <v>196</v>
       </c>
@@ -3785,54 +2739,59 @@
         <v>5.258</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2">
       <c r="A198">
         <v>197</v>
       </c>
       <c r="B198">
-        <v>6.1390000000000002</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.139</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
       <c r="A199">
         <v>198</v>
       </c>
       <c r="B199">
-        <v>7.5049999999999999</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.505</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
       <c r="A200">
         <v>199</v>
       </c>
       <c r="B200">
-        <v>5.8079999999999998</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.808</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
       <c r="A201">
         <v>200</v>
       </c>
       <c r="B201">
-        <v>4.8440000000000003</v>
+        <v>4.844</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="Q1:Q201">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(Q1))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q201"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3863,22 +2822,22 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="Q1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>16.504000000000001</v>
+        <v>16.504</v>
       </c>
       <c r="E2">
         <v>4.18</v>
@@ -3893,434 +2852,194 @@
         <v>3.889935694495676</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" cm="1">
-        <f t="array" ref="K2:K22">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2,J2)</f>
-        <v>4</v>
+        <f t="array" ref="K2">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2,J2)</f>
+        <v>0</v>
       </c>
       <c r="L2" cm="1">
-        <f t="array" ref="L2:L22">(_xlfn.ANCHORARRAY(Q2)+_xlfn.ANCHORARRAY(K2))/2</f>
-        <v>4.5</v>
+        <f t="array" ref="L2">(_xlfn.ANCHORARRAY(Q2)+_xlfn.ANCHORARRAY(K2))/2</f>
+        <v>0</v>
       </c>
       <c r="M2" cm="1">
-        <f t="array" ref="M2:M22">COUNTIFS(B2:B201, "&gt;="&amp;(_xlfn.ANCHORARRAY(K2)-$J$2), B2:B201, "&lt;"&amp;_xlfn.ANCHORARRAY(K2))</f>
+        <f t="array" ref="M2">COUNTIFS(B2:B201, "&gt;="&amp;(_xlfn.ANCHORARRAY(K2)-$J$2), B2:B201, "&lt;"&amp;_xlfn.ANCHORARRAY(K2))</f>
         <v>0</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="2">
         <f>FLOOR(E2,J2)</f>
-        <v>4</v>
-      </c>
-      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
         <f>CEILING(F2,J2)</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q2" cm="1">
-        <f t="array" ref="Q2:Q22">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="array" ref="Q2">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>10.012</v>
       </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>5.5</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-      <c r="Q3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>11.888</v>
       </c>
-      <c r="K4">
-        <v>6</v>
-      </c>
-      <c r="L4">
-        <v>6.5</v>
-      </c>
-      <c r="M4">
-        <v>14</v>
-      </c>
-      <c r="Q4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>8.5359999999999996</v>
-      </c>
-      <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>7.5</v>
-      </c>
-      <c r="M5">
-        <v>17</v>
-      </c>
-      <c r="Q5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>8.536</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>6.5970000000000004</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>8.5</v>
-      </c>
-      <c r="M6">
-        <v>15</v>
-      </c>
-      <c r="Q6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <v>6.597</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>14.867000000000001</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>9.5</v>
-      </c>
-      <c r="M7">
-        <v>23</v>
-      </c>
-      <c r="Q7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <v>14.867</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>10.012</v>
       </c>
-      <c r="K8">
-        <v>10</v>
-      </c>
-      <c r="L8">
-        <v>10.5</v>
-      </c>
-      <c r="M8">
-        <v>17</v>
-      </c>
-      <c r="Q8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>8.4209999999999994</v>
-      </c>
-      <c r="K9">
-        <v>11</v>
-      </c>
-      <c r="L9">
-        <v>11.5</v>
-      </c>
-      <c r="M9">
-        <v>16</v>
-      </c>
-      <c r="Q9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>8.420999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>16.841000000000001</v>
-      </c>
-      <c r="K10">
-        <v>12</v>
-      </c>
-      <c r="L10">
-        <v>12.5</v>
-      </c>
-      <c r="M10">
-        <v>14</v>
-      </c>
-      <c r="Q10">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <v>16.841</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>13.451000000000001</v>
-      </c>
-      <c r="K11">
-        <v>13</v>
-      </c>
-      <c r="L11">
-        <v>13.5</v>
-      </c>
-      <c r="M11">
-        <v>19</v>
-      </c>
-      <c r="Q11">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>13.451</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
         <v>10.946</v>
       </c>
-      <c r="K12">
-        <v>14</v>
-      </c>
-      <c r="L12">
-        <v>14.5</v>
-      </c>
-      <c r="M12">
-        <v>22</v>
-      </c>
-      <c r="Q12">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
         <v>14.702</v>
       </c>
-      <c r="K13">
-        <v>15</v>
-      </c>
-      <c r="L13">
-        <v>15.5</v>
-      </c>
-      <c r="M13">
-        <v>12</v>
-      </c>
-      <c r="Q13">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>16.681000000000001</v>
-      </c>
-      <c r="K14">
-        <v>16</v>
-      </c>
-      <c r="L14">
-        <v>16.5</v>
-      </c>
-      <c r="M14">
-        <v>9</v>
-      </c>
-      <c r="Q14">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+        <v>16.681</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
         <v>10.012</v>
       </c>
-      <c r="K15">
-        <v>17</v>
-      </c>
-      <c r="L15">
-        <v>17.5</v>
-      </c>
-      <c r="M15">
-        <v>6</v>
-      </c>
-      <c r="Q15">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>5.6379999999999999</v>
-      </c>
-      <c r="K16">
-        <v>18</v>
-      </c>
-      <c r="L16">
-        <v>18.5</v>
-      </c>
-      <c r="M16">
-        <v>4</v>
-      </c>
-      <c r="Q16">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5.638</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>8.4499999999999993</v>
-      </c>
-      <c r="K17">
-        <v>19</v>
-      </c>
-      <c r="L17">
-        <v>19.5</v>
-      </c>
-      <c r="M17">
-        <v>2</v>
-      </c>
-      <c r="Q17">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>9.8149999999999995</v>
-      </c>
-      <c r="K18">
-        <v>20</v>
-      </c>
-      <c r="L18">
-        <v>20.5</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="Q18">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <v>9.815</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>7.4340000000000002</v>
-      </c>
-      <c r="K19">
-        <v>21</v>
-      </c>
-      <c r="L19">
-        <v>21.5</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="Q19">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+        <v>7.434</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>8.1549999999999994</v>
-      </c>
-      <c r="K20">
-        <v>22</v>
-      </c>
-      <c r="L20">
-        <v>22.5</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="Q20">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+        <v>8.154999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
         <v>11.057</v>
       </c>
-      <c r="K21">
-        <v>23</v>
-      </c>
-      <c r="L21">
-        <v>23.5</v>
-      </c>
-      <c r="M21">
-        <v>2</v>
-      </c>
-      <c r="Q21">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>8.5069999999999997</v>
-      </c>
-      <c r="K22">
-        <v>24</v>
-      </c>
-      <c r="L22">
-        <v>24.5</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-      <c r="Q22">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+        <v>8.507</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4328,7 +3047,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4336,7 +3055,7 @@
         <v>14.16</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4344,15 +3063,15 @@
         <v>11.276</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>12.606999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+        <v>12.607</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4360,7 +3079,7 @@
         <v>13.933</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4368,31 +3087,31 @@
         <v>14.818</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29">
-        <v>12.606999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+        <v>12.607</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30">
-        <v>8.4209999999999994</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+        <v>8.420999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31">
-        <v>12.451000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+        <v>12.451</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4400,47 +3119,47 @@
         <v>19.692</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33">
-        <v>22.777999999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22.778</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34">
-        <v>16.577999999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16.578</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35">
-        <v>7.7240000000000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.724</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36">
-        <v>11.638999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11.639</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37">
-        <v>10.396000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.396</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4448,55 +3167,55 @@
         <v>14.552</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39">
-        <v>5.0910000000000002</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.091</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40">
-        <v>4.4779999999999998</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.478</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41">
-        <v>22.257000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22.257</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42">
-        <v>12.451000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12.451</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43">
-        <v>14.867000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14.867</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44">
-        <v>9.7149999999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.715</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4504,15 +3223,15 @@
         <v>14.834</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46">
-        <v>9.0909999999999993</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.090999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4520,23 +3239,23 @@
         <v>12.587</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48">
-        <v>9.1180000000000003</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49">
-        <v>21.542999999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+        <v>21.543</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4544,7 +3263,7 @@
         <v>23.288</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4552,15 +3271,15 @@
         <v>10.012</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52">
-        <v>6.5970000000000004</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.597</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4568,23 +3287,23 @@
         <v>13.775</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54">
-        <v>17.923999999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17.924</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55">
-        <v>13.986000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13.986</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4592,15 +3311,15 @@
         <v>15.823</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57">
-        <v>7.9119999999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.912</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4608,23 +3327,23 @@
         <v>11.211</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59">
-        <v>6.2549999999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.255</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60">
-        <v>13.986000000000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13.986</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4632,7 +3351,7 @@
         <v>15.637</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4640,7 +3359,7 @@
         <v>11.276</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4648,39 +3367,39 @@
         <v>12.509</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64">
-        <v>5.6379999999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.638</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65">
-        <v>14.055999999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14.056</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66">
-        <v>8.1549999999999994</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.154999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67">
-        <v>8.7620000000000005</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.762</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4688,23 +3407,23 @@
         <v>13.881</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69">
-        <v>13.287000000000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13.287</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70">
-        <v>13.138999999999999</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13.139</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4712,31 +3431,31 @@
         <v>13.792</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72">
-        <v>17.271000000000001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17.271</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73">
-        <v>8.4209999999999994</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.420999999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74">
-        <v>13.194000000000001</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13.194</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4744,7 +3463,7 @@
         <v>10.49</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4752,31 +3471,31 @@
         <v>16.622</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77">
-        <v>16.504000000000001</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16.504</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78">
-        <v>12.606999999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12.607</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79">
-        <v>5.0910000000000002</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.091</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4784,23 +3503,23 @@
         <v>13.881</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81">
-        <v>8.3919999999999995</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.391999999999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82">
-        <v>9.89</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.890000000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4808,31 +3527,31 @@
         <v>10.946</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84">
-        <v>5.6379999999999999</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.638</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85">
-        <v>7.8179999999999996</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.818</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86">
-        <v>17.608000000000001</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17.608</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4840,31 +3559,31 @@
         <v>14.818</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88">
-        <v>6.2939999999999996</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.294</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89">
-        <v>7.9729999999999999</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.973</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90">
-        <v>7.8179999999999996</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.818</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -4872,7 +3591,7 @@
         <v>12.006</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -4880,7 +3599,7 @@
         <v>12.61</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -4888,15 +3607,15 @@
         <v>11.39</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94">
-        <v>9.1289999999999996</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.129</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -4904,7 +3623,7 @@
         <v>15.494</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4912,7 +3631,7 @@
         <v>11.74</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -4920,7 +3639,7 @@
         <v>15.334</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -4928,15 +3647,15 @@
         <v>15.711</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99">
-        <v>12.821999999999999</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12.822</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -4944,7 +3663,7 @@
         <v>12.099</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -4952,7 +3671,7 @@
         <v>12.099</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -4960,23 +3679,23 @@
         <v>8.827</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2">
       <c r="A103">
         <v>102</v>
       </c>
       <c r="B103">
-        <v>11.409000000000001</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11.409</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104">
-        <v>9.3239999999999998</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.324</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -4984,7 +3703,7 @@
         <v>13.237</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -4992,39 +3711,39 @@
         <v>13.689</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107">
-        <v>13.031000000000001</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13.031</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108">
-        <v>18.696000000000002</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18.696</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
       <c r="A109">
         <v>108</v>
       </c>
       <c r="B109">
-        <v>17.655000000000001</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17.655</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110">
-        <v>11.874000000000001</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11.874</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -5032,7 +3751,7 @@
         <v>13.423</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2">
       <c r="A112">
         <v>111</v>
       </c>
@@ -5040,31 +3759,31 @@
         <v>12.962</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113">
-        <v>14.826000000000001</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14.826</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114">
-        <v>11.547000000000001</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11.547</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115">
-        <v>8.7509999999999994</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.750999999999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
       <c r="A116">
         <v>115</v>
       </c>
@@ -5072,7 +3791,7 @@
         <v>12.538</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2">
       <c r="A117">
         <v>116</v>
       </c>
@@ -5080,15 +3799,15 @@
         <v>14.221</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118">
-        <v>20.190000000000001</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+        <v>20.19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
       <c r="A119">
         <v>118</v>
       </c>
@@ -5096,15 +3815,15 @@
         <v>15.304</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120">
-        <v>10.821999999999999</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.822</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
       <c r="A121">
         <v>120</v>
       </c>
@@ -5112,7 +3831,7 @@
         <v>13.288</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2">
       <c r="A122">
         <v>121</v>
       </c>
@@ -5120,47 +3839,47 @@
         <v>13.186</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2">
       <c r="A123">
         <v>122</v>
       </c>
       <c r="B123">
-        <v>5.1109999999999998</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.111</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
       <c r="A124">
         <v>123</v>
       </c>
       <c r="B124">
-        <v>10.244999999999999</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.245</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
       <c r="A125">
         <v>124</v>
       </c>
       <c r="B125">
-        <v>10.244999999999999</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.245</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126">
-        <v>8.7509999999999994</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.750999999999999</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
       <c r="A127">
         <v>126</v>
       </c>
       <c r="B127">
-        <v>8.9619999999999997</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.962</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
       <c r="A128">
         <v>127</v>
       </c>
@@ -5168,7 +3887,7 @@
         <v>6.68</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2">
       <c r="A129">
         <v>128</v>
       </c>
@@ -5176,23 +3895,23 @@
         <v>10.862</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2">
       <c r="A130">
         <v>129</v>
       </c>
       <c r="B130">
-        <v>8.0500000000000007</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.050000000000001</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
       <c r="A131">
         <v>130</v>
       </c>
       <c r="B131">
-        <v>8.7409999999999997</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.741</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
       <c r="A132">
         <v>131</v>
       </c>
@@ -5200,47 +3919,47 @@
         <v>11.95</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2">
       <c r="A133">
         <v>132</v>
       </c>
       <c r="B133">
-        <v>9.9019999999999992</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.901999999999999</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
       <c r="A134">
         <v>133</v>
       </c>
       <c r="B134">
-        <v>14.542999999999999</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14.543</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
       <c r="A135">
         <v>134</v>
       </c>
       <c r="B135">
-        <v>7.6920000000000002</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.692</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
       <c r="A136">
         <v>135</v>
       </c>
       <c r="B136">
-        <v>7.8179999999999996</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.818</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
       <c r="A137">
         <v>136</v>
       </c>
       <c r="B137">
-        <v>6.9930000000000003</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.993</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
       <c r="A138">
         <v>137</v>
       </c>
@@ -5248,7 +3967,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2">
       <c r="A139">
         <v>138</v>
       </c>
@@ -5256,127 +3975,127 @@
         <v>11.211</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2">
       <c r="A140">
         <v>139</v>
       </c>
       <c r="B140">
-        <v>6.6429999999999998</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.643</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
       <c r="A141">
         <v>140</v>
       </c>
       <c r="B141">
-        <v>5.9850000000000003</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.985</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
       <c r="A142">
         <v>141</v>
       </c>
       <c r="B142">
-        <v>8.0719999999999992</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.071999999999999</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
       <c r="A143">
         <v>142</v>
       </c>
       <c r="B143">
-        <v>5.9850000000000003</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.985</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
       <c r="A144">
         <v>143</v>
       </c>
       <c r="B144">
-        <v>5.2450000000000001</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.245</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
       <c r="A145">
         <v>144</v>
       </c>
       <c r="B145">
-        <v>5.5279999999999996</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.528</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
       <c r="A146">
         <v>145</v>
       </c>
       <c r="B146">
-        <v>8.2889999999999997</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.289</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
       <c r="A147">
         <v>146</v>
       </c>
       <c r="B147">
-        <v>6.8959999999999999</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.896</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
       <c r="A148">
         <v>147</v>
       </c>
       <c r="B148">
-        <v>9.7899999999999991</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.789999999999999</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
       <c r="A149">
         <v>148</v>
       </c>
       <c r="B149">
-        <v>6.5039999999999996</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.504</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
       <c r="A150">
         <v>149</v>
       </c>
       <c r="B150">
-        <v>5.3369999999999997</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.337</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
       <c r="A151">
         <v>150</v>
       </c>
       <c r="B151">
-        <v>9.6199999999999992</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.619999999999999</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
       <c r="A152">
         <v>151</v>
       </c>
       <c r="B152">
-        <v>9.9019999999999992</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.901999999999999</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
       <c r="A153">
         <v>152</v>
       </c>
       <c r="B153">
-        <v>6.1059999999999999</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.106</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
       <c r="A154">
         <v>153</v>
       </c>
       <c r="B154">
-        <v>8.9139999999999997</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.914</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
       <c r="A155">
         <v>154</v>
       </c>
@@ -5384,31 +4103,31 @@
         <v>7.351</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2">
       <c r="A156">
         <v>155</v>
       </c>
       <c r="B156">
-        <v>8.7409999999999997</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.741</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
       <c r="A157">
         <v>156</v>
       </c>
       <c r="B157">
-        <v>7.8179999999999996</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.818</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
       <c r="A158">
         <v>157</v>
       </c>
       <c r="B158">
-        <v>7.9729999999999999</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.973</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
       <c r="A159">
         <v>158</v>
       </c>
@@ -5416,47 +4135,47 @@
         <v>12.994</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2">
       <c r="A160">
         <v>159</v>
       </c>
       <c r="B160">
-        <v>9.1980000000000004</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.198</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
       <c r="A161">
         <v>160</v>
       </c>
       <c r="B161">
-        <v>9.1980000000000004</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.198</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
       <c r="A162">
         <v>161</v>
       </c>
       <c r="B162">
-        <v>9.5440000000000005</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.544</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
       <c r="A163">
         <v>162</v>
       </c>
       <c r="B163">
-        <v>12.635999999999999</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12.636</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
       <c r="A164">
         <v>163</v>
       </c>
       <c r="B164">
-        <v>15.707000000000001</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15.707</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
       <c r="A165">
         <v>164</v>
       </c>
@@ -5464,15 +4183,15 @@
         <v>12.727</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2">
       <c r="A166">
         <v>165</v>
       </c>
       <c r="B166">
-        <v>13.925000000000001</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13.925</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
       <c r="A167">
         <v>166</v>
       </c>
@@ -5480,7 +4199,7 @@
         <v>11.211</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2">
       <c r="A168">
         <v>167</v>
       </c>
@@ -5488,15 +4207,15 @@
         <v>6.726</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2">
       <c r="A169">
         <v>168</v>
       </c>
       <c r="B169">
-        <v>15.265000000000001</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15.265</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
       <c r="A170">
         <v>169</v>
       </c>
@@ -5504,15 +4223,15 @@
         <v>12.137</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2">
       <c r="A171">
         <v>170</v>
       </c>
       <c r="B171">
-        <v>10.702999999999999</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.703</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
       <c r="A172">
         <v>171</v>
       </c>
@@ -5520,31 +4239,31 @@
         <v>15.039</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2">
       <c r="A173">
         <v>172</v>
       </c>
       <c r="B173">
-        <v>7.6360000000000001</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.636</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
       <c r="A174">
         <v>173</v>
       </c>
       <c r="B174">
-        <v>9.7210000000000001</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.721</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
       <c r="A175">
         <v>174</v>
       </c>
       <c r="B175">
-        <v>9.8149999999999995</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.815</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
       <c r="A176">
         <v>175</v>
       </c>
@@ -5552,7 +4271,7 @@
         <v>13.881</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2">
       <c r="A177">
         <v>176</v>
       </c>
@@ -5560,31 +4279,31 @@
         <v>18.849</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2">
       <c r="A178">
         <v>177</v>
       </c>
       <c r="B178">
-        <v>13.986000000000001</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13.986</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
       <c r="A179">
         <v>178</v>
       </c>
       <c r="B179">
-        <v>12.494999999999999</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12.495</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
       <c r="A180">
         <v>179</v>
       </c>
       <c r="B180">
-        <v>6.9669999999999996</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.967</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
       <c r="A181">
         <v>180</v>
       </c>
@@ -5592,7 +4311,7 @@
         <v>10.634</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2">
       <c r="A182">
         <v>181</v>
       </c>
@@ -5600,7 +4319,7 @@
         <v>13.712</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2">
       <c r="A183">
         <v>182</v>
       </c>
@@ -5608,39 +4327,39 @@
         <v>13.815</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2">
       <c r="A184">
         <v>183</v>
       </c>
       <c r="B184">
-        <v>6.7380000000000004</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.738</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
       <c r="A185">
         <v>184</v>
       </c>
       <c r="B185">
-        <v>8.9250000000000007</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.925000000000001</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
       <c r="A186">
         <v>185</v>
       </c>
       <c r="B186">
-        <v>7.3410000000000002</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.341</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
       <c r="A187">
         <v>186</v>
       </c>
       <c r="B187">
-        <v>6.7759999999999998</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.776</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
       <c r="A188">
         <v>187</v>
       </c>
@@ -5648,39 +4367,39 @@
         <v>5.032</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2">
       <c r="A189">
         <v>188</v>
       </c>
       <c r="B189">
-        <v>6.7850000000000001</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.785</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
       <c r="A190">
         <v>189</v>
       </c>
       <c r="B190">
-        <v>6.6280000000000001</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.628</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
       <c r="A191">
         <v>190</v>
       </c>
       <c r="B191">
-        <v>7.4269999999999996</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.427</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
       <c r="A192">
         <v>191</v>
       </c>
       <c r="B192">
-        <v>8.2720000000000002</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.272</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
       <c r="A193">
         <v>192</v>
       </c>
@@ -5688,7 +4407,7 @@
         <v>10.025</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2">
       <c r="A194">
         <v>193</v>
       </c>
@@ -5696,7 +4415,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2">
       <c r="A195">
         <v>194</v>
       </c>
@@ -5704,23 +4423,23 @@
         <v>5.556</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2">
       <c r="A196">
         <v>195</v>
       </c>
       <c r="B196">
-        <v>5.3029999999999999</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.303</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
       <c r="A197">
         <v>196</v>
       </c>
       <c r="B197">
-        <v>8.8529999999999998</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.853</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
       <c r="A198">
         <v>197</v>
       </c>
@@ -5728,15 +4447,15 @@
         <v>10.366</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2">
       <c r="A199">
         <v>198</v>
       </c>
       <c r="B199">
-        <v>6.0019999999999998</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.002</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
       <c r="A200">
         <v>199</v>
       </c>
@@ -5744,31 +4463,35 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2">
       <c r="A201">
         <v>200</v>
       </c>
       <c r="B201">
-        <v>9.8610000000000007</v>
+        <v>9.861000000000001</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="Q1:Q201">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(Q1))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q201"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5799,17 +4522,17 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="Q1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5817,474 +4540,222 @@
         <v>12.05</v>
       </c>
       <c r="E2">
-        <v>2.2389999999999999</v>
+        <v>2.239</v>
       </c>
       <c r="F2">
-        <v>22.015000000000001</v>
+        <v>22.015</v>
       </c>
       <c r="G2">
-        <v>7.9515000000000011</v>
+        <v>7.951500000000001</v>
       </c>
       <c r="H2">
-        <v>2.9333624933833078</v>
+        <v>2.933362493383308</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" cm="1">
-        <f t="array" ref="K2:K23">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2,J2)</f>
-        <v>2</v>
+        <f t="array" ref="K2">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2,J2)</f>
+        <v>0</v>
       </c>
       <c r="L2" cm="1">
-        <f t="array" ref="L2:L23">(_xlfn.ANCHORARRAY(Q2)+_xlfn.ANCHORARRAY(K2))/2</f>
-        <v>2.5</v>
+        <f t="array" ref="L2">(_xlfn.ANCHORARRAY(Q2)+_xlfn.ANCHORARRAY(K2))/2</f>
+        <v>0</v>
       </c>
       <c r="M2" cm="1">
-        <f t="array" ref="M2:M23">COUNTIFS(B2:B201, "&gt;="&amp;(_xlfn.ANCHORARRAY(K2)-$J$2), B2:B201, "&lt;"&amp;_xlfn.ANCHORARRAY(K2))</f>
+        <f t="array" ref="M2">COUNTIFS(B2:B201, "&gt;="&amp;(_xlfn.ANCHORARRAY(K2)-$J$2), B2:B201, "&lt;"&amp;_xlfn.ANCHORARRAY(K2))</f>
         <v>0</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="2">
         <f>FLOOR(E2,J2)</f>
-        <v>2</v>
-      </c>
-      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
         <f>CEILING(F2,J2)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q2" cm="1">
-        <f t="array" ref="Q2:Q23">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="array" ref="Q2">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>16.247</v>
       </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>3.5</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-      <c r="Q3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4.4059999999999997</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>4.5</v>
-      </c>
-      <c r="M4">
-        <v>7</v>
-      </c>
-      <c r="Q4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <v>4.406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>4.4809999999999999</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>5.5</v>
-      </c>
-      <c r="M5">
-        <v>13</v>
-      </c>
-      <c r="Q5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>4.481</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>3.1859999999999999</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>6.5</v>
-      </c>
-      <c r="M6">
-        <v>28</v>
-      </c>
-      <c r="Q6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <v>3.186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3.3239999999999998</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>7.5</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
-      </c>
-      <c r="Q7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <v>3.324</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>5.633</v>
       </c>
-      <c r="K8">
-        <v>8</v>
-      </c>
-      <c r="L8">
-        <v>8.5</v>
-      </c>
-      <c r="M8">
-        <v>33</v>
-      </c>
-      <c r="Q8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>7.4020000000000001</v>
-      </c>
-      <c r="K9">
-        <v>9</v>
-      </c>
-      <c r="L9">
-        <v>9.5</v>
-      </c>
-      <c r="M9">
-        <v>24</v>
-      </c>
-      <c r="Q9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>7.402</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>9.0210000000000008</v>
-      </c>
-      <c r="K10">
-        <v>10</v>
-      </c>
-      <c r="L10">
-        <v>10.5</v>
-      </c>
-      <c r="M10">
-        <v>21</v>
-      </c>
-      <c r="Q10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <v>9.021000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>4.8869999999999996</v>
-      </c>
-      <c r="K11">
-        <v>11</v>
-      </c>
-      <c r="L11">
-        <v>11.5</v>
-      </c>
-      <c r="M11">
-        <v>14</v>
-      </c>
-      <c r="Q11">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>4.887</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
         <v>5.31</v>
       </c>
-      <c r="K12">
-        <v>12</v>
-      </c>
-      <c r="L12">
-        <v>12.5</v>
-      </c>
-      <c r="M12">
-        <v>10</v>
-      </c>
-      <c r="Q12">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7.1989999999999998</v>
-      </c>
-      <c r="K13">
-        <v>13</v>
-      </c>
-      <c r="L13">
-        <v>13.5</v>
-      </c>
-      <c r="M13">
-        <v>7</v>
-      </c>
-      <c r="Q13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <v>7.199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>6.8940000000000001</v>
-      </c>
-      <c r="K14">
-        <v>14</v>
-      </c>
-      <c r="L14">
-        <v>14.5</v>
-      </c>
-      <c r="M14">
-        <v>5</v>
-      </c>
-      <c r="Q14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+        <v>6.894</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>5.2629999999999999</v>
-      </c>
-      <c r="K15">
-        <v>15</v>
-      </c>
-      <c r="L15">
-        <v>15.5</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="Q15">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5.263</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>5.9649999999999999</v>
-      </c>
-      <c r="K16">
-        <v>16</v>
-      </c>
-      <c r="L16">
-        <v>16.5</v>
-      </c>
-      <c r="M16">
-        <v>2</v>
-      </c>
-      <c r="Q16">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5.965</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>5.9649999999999999</v>
-      </c>
-      <c r="K17">
-        <v>17</v>
-      </c>
-      <c r="L17">
-        <v>17.5</v>
-      </c>
-      <c r="M17">
-        <v>2</v>
-      </c>
-      <c r="Q17">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5.965</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>8.4870000000000001</v>
-      </c>
-      <c r="K18">
-        <v>18</v>
-      </c>
-      <c r="L18">
-        <v>18.5</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <v>8.487</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>5.9749999999999996</v>
-      </c>
-      <c r="K19">
-        <v>19</v>
-      </c>
-      <c r="L19">
-        <v>19.5</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5.975</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>7.1050000000000004</v>
-      </c>
-      <c r="K20">
-        <v>20</v>
-      </c>
-      <c r="L20">
-        <v>20.5</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+        <v>7.105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>7.0259999999999998</v>
-      </c>
-      <c r="K21">
-        <v>21</v>
-      </c>
-      <c r="L21">
-        <v>21.5</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+        <v>7.026</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
         <v>7.157</v>
       </c>
-      <c r="K22">
-        <v>22</v>
-      </c>
-      <c r="L22">
-        <v>22.5</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>7.7670000000000003</v>
-      </c>
-      <c r="K23">
-        <v>23</v>
-      </c>
-      <c r="L23">
-        <v>23.5</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-      <c r="Q23">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+        <v>7.767</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2.2469999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+        <v>2.247</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6292,7 +4763,7 @@
         <v>5.109</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6300,7 +4771,7 @@
         <v>11.664</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6308,15 +4779,15 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
-        <v>8.1389999999999993</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+        <v>8.138999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -6324,23 +4795,23 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30">
-        <v>5.6580000000000004</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5.658</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31">
-        <v>6.9109999999999996</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+        <v>6.911</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6348,47 +4819,47 @@
         <v>5.492</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33">
-        <v>6.7030000000000003</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.703</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34">
-        <v>7.3010000000000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.301</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35">
-        <v>7.5010000000000003</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.501</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36">
-        <v>7.5579999999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.558</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37">
-        <v>8.9939999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.994</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6396,87 +4867,87 @@
         <v>12.651</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39">
-        <v>9.1029999999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.103</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40">
-        <v>6.8940000000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.894</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41">
-        <v>5.2160000000000002</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.216</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42">
-        <v>8.1010000000000009</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.101000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43">
-        <v>8.4280000000000008</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.428000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44">
-        <v>4.0010000000000003</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45">
-        <v>7.3010000000000002</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.301</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46">
-        <v>7.8460000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.846</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47">
-        <v>8.0009999999999994</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.000999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48">
-        <v>6.4029999999999996</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.403</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6484,23 +4955,23 @@
         <v>5.024</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50">
-        <v>6.1280000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.128</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51">
-        <v>8.1910000000000007</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.191000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6508,15 +4979,15 @@
         <v>5.024</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53">
-        <v>3.5089999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.509</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6524,47 +4995,47 @@
         <v>10.218</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55">
-        <v>6.2249999999999996</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.225</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56">
-        <v>7.6760000000000002</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.676</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57">
-        <v>4.5990000000000002</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.599</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58">
-        <v>12.451000000000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12.451</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59">
-        <v>7.0709999999999997</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.071</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6572,39 +5043,39 @@
         <v>7.74</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61">
-        <v>6.3810000000000002</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.381</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62">
-        <v>5.9749999999999996</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.975</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63">
-        <v>7.2759999999999998</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.276</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64">
-        <v>2.2389999999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.239</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6612,15 +5083,15 @@
         <v>2.819</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66">
-        <v>4.9450000000000003</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.945</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6628,39 +5099,39 @@
         <v>6.016</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68">
-        <v>2.7970000000000002</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2.797</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69">
-        <v>3.7170000000000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.717</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70">
-        <v>10.396000000000001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.396</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71">
-        <v>5.3490000000000002</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.349</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6668,15 +5139,15 @@
         <v>10.634</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73">
-        <v>9.2309999999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.231</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6684,31 +5155,31 @@
         <v>11.057</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75">
-        <v>6.7169999999999996</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.717</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76">
-        <v>8.0719999999999992</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.071999999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77">
-        <v>4.7560000000000002</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.756</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6716,7 +5187,7 @@
         <v>12.416</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6724,23 +5195,23 @@
         <v>12.238</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80">
-        <v>6.4470000000000001</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.447</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81">
-        <v>9.6959999999999997</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.696</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6748,47 +5219,47 @@
         <v>15.337</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83">
-        <v>5.5940000000000003</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.594</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84">
-        <v>11.287000000000001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11.287</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85">
-        <v>4.5449999999999999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.545</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86">
-        <v>9.4079999999999995</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.407999999999999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87">
-        <v>9.1509999999999998</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.151</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6796,7 +5267,7 @@
         <v>2.819</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -6804,47 +5275,47 @@
         <v>5.944</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90">
-        <v>10.236000000000001</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.236</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91">
-        <v>6.5970000000000004</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.597</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92">
-        <v>6.2549999999999999</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.255</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93">
-        <v>6.2549999999999999</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.255</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94">
-        <v>8.4060000000000006</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.406000000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -6852,111 +5323,111 @@
         <v>11.112</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96">
-        <v>6.5970000000000004</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.597</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97">
-        <v>13.701000000000001</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13.701</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98">
-        <v>7.5650000000000004</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.565</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99">
-        <v>5.9950000000000001</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.995</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100">
-        <v>3.8279999999999998</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.828</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101">
-        <v>5.4550000000000001</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.455</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102">
-        <v>10.848000000000001</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.848</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
       <c r="A103">
         <v>102</v>
       </c>
       <c r="B103">
-        <v>5.1749999999999998</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.175</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104">
-        <v>5.8209999999999997</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.821</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105">
-        <v>5.9950000000000001</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.995</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106">
-        <v>6.4189999999999996</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.419</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107">
-        <v>7.7889999999999997</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.789</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108">
-        <v>9.1029999999999998</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.103</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6964,23 +5435,23 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110">
-        <v>14.646000000000001</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14.646</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111">
-        <v>9.8520000000000003</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.852</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6988,7 +5459,7 @@
         <v>13.06</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6996,7 +5467,7 @@
         <v>11.503</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2">
       <c r="A114">
         <v>113</v>
       </c>
@@ -7004,39 +5475,39 @@
         <v>4.306</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115">
-        <v>6.2930000000000001</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.293</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116">
-        <v>4.3330000000000002</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.333</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
       <c r="A117">
         <v>116</v>
       </c>
       <c r="B117">
-        <v>5.0860000000000003</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.086</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118">
-        <v>3.9460000000000002</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.946</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
       <c r="A119">
         <v>118</v>
       </c>
@@ -7044,31 +5515,31 @@
         <v>13.138</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120">
-        <v>4.4109999999999996</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.411</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121">
-        <v>10.920999999999999</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.921</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
       <c r="A122">
         <v>121</v>
       </c>
       <c r="B122">
-        <v>9.1910000000000007</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.191000000000001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
       <c r="A123">
         <v>122</v>
       </c>
@@ -7076,55 +5547,55 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2">
       <c r="A124">
         <v>123</v>
       </c>
       <c r="B124">
-        <v>7.2880000000000003</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.288</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
       <c r="A125">
         <v>124</v>
       </c>
       <c r="B125">
-        <v>6.2930000000000001</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.293</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126">
-        <v>3.8279999999999998</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.828</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
       <c r="A127">
         <v>126</v>
       </c>
       <c r="B127">
-        <v>13.430999999999999</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13.431</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
       <c r="A128">
         <v>127</v>
       </c>
       <c r="B128">
-        <v>22.015000000000001</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22.015</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
       <c r="A129">
         <v>128</v>
       </c>
       <c r="B129">
-        <v>5.2629999999999999</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.263</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
       <c r="A130">
         <v>129</v>
       </c>
@@ -7132,63 +5603,63 @@
         <v>4.306</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2">
       <c r="A131">
         <v>130</v>
       </c>
       <c r="B131">
-        <v>10.920999999999999</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.921</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
       <c r="A132">
         <v>131</v>
       </c>
       <c r="B132">
-        <v>8.1479999999999997</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.148</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
       <c r="A133">
         <v>132</v>
       </c>
       <c r="B133">
-        <v>9.2409999999999997</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.241</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
       <c r="A134">
         <v>133</v>
       </c>
       <c r="B134">
-        <v>8.0210000000000008</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.021000000000001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
       <c r="A135">
         <v>134</v>
       </c>
       <c r="B135">
-        <v>7.7149999999999999</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.715</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
       <c r="A136">
         <v>135</v>
       </c>
       <c r="B136">
-        <v>5.4550000000000001</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.455</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
       <c r="A137">
         <v>136</v>
       </c>
       <c r="B137">
-        <v>6.7160000000000002</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.716</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
       <c r="A138">
         <v>137</v>
       </c>
@@ -7196,55 +5667,55 @@
         <v>6.508</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2">
       <c r="A139">
         <v>138</v>
       </c>
       <c r="B139">
-        <v>7.9889999999999999</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.989</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
       <c r="A140">
         <v>139</v>
       </c>
       <c r="B140">
-        <v>6.9669999999999996</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.967</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
       <c r="A141">
         <v>140</v>
       </c>
       <c r="B141">
-        <v>9.0709999999999997</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.071</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
       <c r="A142">
         <v>141</v>
       </c>
       <c r="B142">
-        <v>9.6199999999999992</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.619999999999999</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
       <c r="A143">
         <v>142</v>
       </c>
       <c r="B143">
-        <v>9.7149999999999999</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.715</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
       <c r="A144">
         <v>143</v>
       </c>
       <c r="B144">
-        <v>7.0709999999999997</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.071</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
       <c r="A145">
         <v>144</v>
       </c>
@@ -7252,7 +5723,7 @@
         <v>7.532</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2">
       <c r="A146">
         <v>145</v>
       </c>
@@ -7260,7 +5731,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2">
       <c r="A147">
         <v>146</v>
       </c>
@@ -7268,23 +5739,23 @@
         <v>7.351</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2">
       <c r="A148">
         <v>147</v>
       </c>
       <c r="B148">
-        <v>9.0709999999999997</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.071</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
       <c r="A149">
         <v>148</v>
       </c>
       <c r="B149">
-        <v>10.396000000000001</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.396</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
       <c r="A150">
         <v>149</v>
       </c>
@@ -7292,71 +5763,71 @@
         <v>6.726</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2">
       <c r="A151">
         <v>150</v>
       </c>
       <c r="B151">
-        <v>9.4149999999999991</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.414999999999999</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
       <c r="A152">
         <v>151</v>
       </c>
       <c r="B152">
-        <v>10.696999999999999</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.697</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
       <c r="A153">
         <v>152</v>
       </c>
       <c r="B153">
-        <v>9.8520000000000003</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.852</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
       <c r="A154">
         <v>153</v>
       </c>
       <c r="B154">
-        <v>11.622999999999999</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11.623</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
       <c r="A155">
         <v>154</v>
       </c>
       <c r="B155">
-        <v>11.872999999999999</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11.873</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
       <c r="A156">
         <v>155</v>
       </c>
       <c r="B156">
-        <v>9.0980000000000008</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.098000000000001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
       <c r="A157">
         <v>156</v>
       </c>
       <c r="B157">
-        <v>7.2080000000000002</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.208</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
       <c r="A158">
         <v>157</v>
       </c>
       <c r="B158">
-        <v>5.8609999999999998</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.861</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
       <c r="A159">
         <v>158</v>
       </c>
@@ -7364,7 +5835,7 @@
         <v>10.946</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2">
       <c r="A160">
         <v>159</v>
       </c>
@@ -7372,23 +5843,23 @@
         <v>11.189</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2">
       <c r="A161">
         <v>160</v>
       </c>
       <c r="B161">
-        <v>5.9850000000000003</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.985</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
       <c r="A162">
         <v>161</v>
       </c>
       <c r="B162">
-        <v>10.582000000000001</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.582</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
       <c r="A163">
         <v>162</v>
       </c>
@@ -7396,7 +5867,7 @@
         <v>5.944</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2">
       <c r="A164">
         <v>163</v>
       </c>
@@ -7404,7 +5875,7 @@
         <v>13.618</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2">
       <c r="A165">
         <v>164</v>
       </c>
@@ -7412,23 +5883,23 @@
         <v>12.587</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2">
       <c r="A166">
         <v>165</v>
       </c>
       <c r="B166">
-        <v>15.135999999999999</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15.136</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
       <c r="A167">
         <v>166</v>
       </c>
       <c r="B167">
-        <v>16.504000000000001</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16.504</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
       <c r="A168">
         <v>167</v>
       </c>
@@ -7436,31 +5907,31 @@
         <v>7.351</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2">
       <c r="A169">
         <v>168</v>
       </c>
       <c r="B169">
-        <v>8.7409999999999997</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.741</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
       <c r="A170">
         <v>169</v>
       </c>
       <c r="B170">
-        <v>9.8960000000000008</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.896000000000001</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
       <c r="A171">
         <v>170</v>
       </c>
       <c r="B171">
-        <v>6.6340000000000003</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.634</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
       <c r="A172">
         <v>171</v>
       </c>
@@ -7468,31 +5939,31 @@
         <v>8.23</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2">
       <c r="A173">
         <v>172</v>
       </c>
       <c r="B173">
-        <v>9.6010000000000009</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.601000000000001</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
       <c r="A174">
         <v>173</v>
       </c>
       <c r="B174">
-        <v>10.771000000000001</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.771</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
       <c r="A175">
         <v>174</v>
       </c>
       <c r="B175">
-        <v>9.3819999999999997</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.382</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
       <c r="A176">
         <v>175</v>
       </c>
@@ -7500,7 +5971,7 @@
         <v>12.416</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2">
       <c r="A177">
         <v>176</v>
       </c>
@@ -7508,7 +5979,7 @@
         <v>10.49</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2">
       <c r="A178">
         <v>177</v>
       </c>
@@ -7516,47 +5987,47 @@
         <v>11.831</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2">
       <c r="A179">
         <v>178</v>
       </c>
       <c r="B179">
-        <v>8.3989999999999991</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.398999999999999</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
       <c r="A180">
         <v>179</v>
       </c>
       <c r="B180">
-        <v>8.1630000000000003</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.163</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
       <c r="A181">
         <v>180</v>
       </c>
       <c r="B181">
-        <v>9.7899999999999991</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.789999999999999</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
       <c r="A182">
         <v>181</v>
       </c>
       <c r="B182">
-        <v>7.0019999999999998</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.002</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
       <c r="A183">
         <v>182</v>
       </c>
       <c r="B183">
-        <v>6.7169999999999996</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.717</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
       <c r="A184">
         <v>183</v>
       </c>
@@ -7564,79 +6035,79 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2">
       <c r="A185">
         <v>184</v>
       </c>
       <c r="B185">
-        <v>4.8570000000000002</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.857</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
       <c r="A186">
         <v>185</v>
       </c>
       <c r="B186">
-        <v>8.0500000000000007</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.050000000000001</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
       <c r="A187">
         <v>186</v>
       </c>
       <c r="B187">
-        <v>8.7479999999999993</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.747999999999999</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
       <c r="A188">
         <v>187</v>
       </c>
       <c r="B188">
-        <v>8.6359999999999992</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.635999999999999</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
       <c r="A189">
         <v>188</v>
       </c>
       <c r="B189">
-        <v>5.4619999999999997</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5.462</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
       <c r="A190">
         <v>189</v>
       </c>
       <c r="B190">
-        <v>8.2520000000000007</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.252000000000001</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
       <c r="A191">
         <v>190</v>
       </c>
       <c r="B191">
-        <v>7.2080000000000002</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.208</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
       <c r="A192">
         <v>191</v>
       </c>
       <c r="B192">
-        <v>11.106999999999999</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11.107</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
       <c r="A193">
         <v>192</v>
       </c>
       <c r="B193">
-        <v>8.1549999999999994</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.154999999999999</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
       <c r="A194">
         <v>193</v>
       </c>
@@ -7644,63 +6115,68 @@
         <v>6.726</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2">
       <c r="A195">
         <v>194</v>
       </c>
       <c r="B195">
-        <v>8.8460000000000001</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.846</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
       <c r="A196">
         <v>195</v>
       </c>
       <c r="B196">
-        <v>7.7629999999999999</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.763</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
       <c r="A197">
         <v>196</v>
       </c>
       <c r="B197">
-        <v>7.7240000000000002</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.724</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
       <c r="A198">
         <v>197</v>
       </c>
       <c r="B198">
-        <v>10.978999999999999</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10.979</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
       <c r="A199">
         <v>198</v>
       </c>
       <c r="B199">
-        <v>7.2759999999999998</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.276</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
       <c r="A200">
         <v>199</v>
       </c>
       <c r="B200">
-        <v>8.3109999999999999</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8.311</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
       <c r="A201">
         <v>200</v>
       </c>
       <c r="B201">
-        <v>8.1549999999999994</v>
+        <v>8.154999999999999</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="Q1:Q201">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(Q1))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/100040000/output.xlsx
+++ b/100040000/output.xlsx
@@ -18,6 +18,12 @@
     <definedName name="frequencies_200122941">200122941!$M$2:INDEX(200122941!$M:$M,2+COUNT(_xlfn.ANCHORARRAY(200122941!$M$2))-1)</definedName>
     <definedName name="frequencies_200122942">200122942!$M$2:INDEX(200122942!$M:$M,2+COUNT(_xlfn.ANCHORARRAY(200122942!$M$2))-1)</definedName>
     <definedName name="frequencies_200122943">200122943!$M$2:INDEX(200122943!$M:$M,2+COUNT(_xlfn.ANCHORARRAY(200122943!$M$2))-1)</definedName>
+    <definedName name="mid_200122941">200122941!$L$2:INDEX(200122941!$L:$L,2+COUNT(_xlfn.ANCHORARRAY(200122941!$L$2))-1)</definedName>
+    <definedName name="mid_200122942">200122942!$L$2:INDEX(200122942!$L:$L,2+COUNT(_xlfn.ANCHORARRAY(200122942!$L$2))-1)</definedName>
+    <definedName name="mid_200122943">200122943!$L$2:INDEX(200122943!$L:$L,2+COUNT(_xlfn.ANCHORARRAY(200122943!$L$2))-1)</definedName>
+    <definedName name="zeros_200122941">200122941!$R$2:INDEX(200122941!$R:$R,2+COUNT(_xlfn.ANCHORARRAY(200122941!$R$2))-1)</definedName>
+    <definedName name="zeros_200122942">200122942!$R$2:INDEX(200122942!$R:$R,2+COUNT(_xlfn.ANCHORARRAY(200122942!$R$2))-1)</definedName>
+    <definedName name="zeros_200122943">200122943!$R$2:INDEX(200122943!$R:$R,2+COUNT(_xlfn.ANCHORARRAY(200122943!$R$2))-1)</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="14">
   <si>
     <t>Particle (N)</t>
   </si>
@@ -86,6 +92,9 @@
   <si>
     <t>data_for_mid_calc</t>
   </si>
+  <si>
+    <t>zeros</t>
+  </si>
 </sst>
 </file>
 
@@ -109,7 +118,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -155,7 +164,7 @@
   <dxfs count="1">
     <dxf>
       <font>
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FF000000"/>
       </font>
     </dxf>
   </dxfs>
@@ -187,15 +196,39 @@
     </c:title>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:cat>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:errBars>
+            <c:errDir val="y"/>
+            <c:errBarType val="minus"/>
+            <c:errValType val="percentage"/>
+            <c:noEndCap val="1"/>
+            <c:val val="100"/>
+            <c:spPr>
+              <a:ln w="127000">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:errBars>
+          <c:xVal>
             <c:strRef>
-              <c:f>200122941!bin_200122941</c:f>
+              <c:f>200122941!mid_200122941</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -203,8 +236,8 @@
                 </c:pt>
               </c:strCache>
             </c:strRef>
-          </c:cat>
-          <c:val>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>200122941!frequencies_200122941</c:f>
               <c:numCache>
@@ -215,60 +248,18 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
+          <c:smooth val="1"/>
         </c:ser>
-        <c:gapWidth val="0"/>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
-      </c:barChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>200122941!bin_200122941</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Particle (N)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>200122941!frequencies_200122941</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:marker val="1"/>
-        <c:axId val="50010001"/>
-        <c:axId val="50010002"/>
-      </c:lineChart>
-      <c:catAx>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="50010001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="18"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:title>
@@ -289,14 +280,14 @@
           </c:tx>
           <c:layout/>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010002"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
+      </c:valAx>
       <c:valAx>
         <c:axId val="50010002"/>
         <c:scaling>
@@ -307,7 +298,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" vert="horz"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -327,7 +318,7 @@
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010001"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -364,15 +355,39 @@
     </c:title>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:cat>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:errBars>
+            <c:errDir val="y"/>
+            <c:errBarType val="minus"/>
+            <c:errValType val="percentage"/>
+            <c:noEndCap val="1"/>
+            <c:val val="100"/>
+            <c:spPr>
+              <a:ln w="152400">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:errBars>
+          <c:xVal>
             <c:strRef>
-              <c:f>200122942!bin_200122942</c:f>
+              <c:f>200122942!mid_200122942</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -380,8 +395,8 @@
                 </c:pt>
               </c:strCache>
             </c:strRef>
-          </c:cat>
-          <c:val>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>200122942!frequencies_200122942</c:f>
               <c:numCache>
@@ -392,60 +407,18 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
+          <c:smooth val="1"/>
         </c:ser>
-        <c:gapWidth val="0"/>
         <c:axId val="50020001"/>
         <c:axId val="50020002"/>
-      </c:barChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>200122942!bin_200122942</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Particle (N)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>200122942!frequencies_200122942</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:marker val="1"/>
-        <c:axId val="50020001"/>
-        <c:axId val="50020002"/>
-      </c:lineChart>
-      <c:catAx>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="50020001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="26"/>
+          <c:min val="4"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:title>
@@ -466,14 +439,14 @@
           </c:tx>
           <c:layout/>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020002"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
+      </c:valAx>
       <c:valAx>
         <c:axId val="50020002"/>
         <c:scaling>
@@ -484,7 +457,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" vert="horz"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -504,7 +477,7 @@
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -541,15 +514,39 @@
     </c:title>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:cat>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:errBars>
+            <c:errDir val="y"/>
+            <c:errBarType val="minus"/>
+            <c:errValType val="percentage"/>
+            <c:noEndCap val="1"/>
+            <c:val val="100"/>
+            <c:spPr>
+              <a:ln w="165100">
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:errBars>
+          <c:xVal>
             <c:strRef>
-              <c:f>200122943!bin_200122943</c:f>
+              <c:f>200122943!mid_200122943</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -557,8 +554,8 @@
                 </c:pt>
               </c:strCache>
             </c:strRef>
-          </c:cat>
-          <c:val>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>200122943!frequencies_200122943</c:f>
               <c:numCache>
@@ -569,60 +566,18 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
+          <c:smooth val="1"/>
         </c:ser>
-        <c:gapWidth val="0"/>
         <c:axId val="50030001"/>
         <c:axId val="50030002"/>
-      </c:barChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>200122943!bin_200122943</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Particle (N)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>200122943!frequencies_200122943</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:marker val="1"/>
-        <c:axId val="50030001"/>
-        <c:axId val="50030002"/>
-      </c:lineChart>
-      <c:catAx>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="50030001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="26"/>
+          <c:min val="2"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:title>
@@ -643,14 +598,14 @@
           </c:tx>
           <c:layout/>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030002"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
+      </c:valAx>
       <c:valAx>
         <c:axId val="50030002"/>
         <c:scaling>
@@ -661,7 +616,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" vert="horz"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -681,7 +636,7 @@
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030001"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1084,14 +1039,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:R201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1131,8 +1086,11 @@
       <c r="Q1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1178,8 +1136,12 @@
         <f t="array" ref="Q2">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" cm="1">
+        <f t="array" ref="R2">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,0,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1187,7 +1149,7 @@
         <v>4.536</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1195,7 +1157,7 @@
         <v>9.909000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1203,7 +1165,7 @@
         <v>6.235</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1211,7 +1173,7 @@
         <v>9.564</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1219,7 +1181,7 @@
         <v>9.977</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1227,7 +1189,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1235,7 +1197,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1243,7 +1205,7 @@
         <v>8.923</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1251,7 +1213,7 @@
         <v>3.112</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1259,7 +1221,7 @@
         <v>9.234</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1267,7 +1229,7 @@
         <v>6.224</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1275,7 +1237,7 @@
         <v>8.118</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1283,7 +1245,7 @@
         <v>6.405</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2784,14 +2746,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:R201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2831,8 +2793,11 @@
       <c r="Q1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2878,8 +2843,12 @@
         <f t="array" ref="Q2">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" cm="1">
+        <f t="array" ref="R2">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,0,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2887,7 +2856,7 @@
         <v>10.012</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2895,7 +2864,7 @@
         <v>11.888</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2903,7 +2872,7 @@
         <v>8.536</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2911,7 +2880,7 @@
         <v>6.597</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2919,7 +2888,7 @@
         <v>14.867</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2927,7 +2896,7 @@
         <v>10.012</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2935,7 +2904,7 @@
         <v>8.420999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2943,7 +2912,7 @@
         <v>16.841</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2951,7 +2920,7 @@
         <v>13.451</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2959,7 +2928,7 @@
         <v>10.946</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2967,7 +2936,7 @@
         <v>14.702</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2975,7 +2944,7 @@
         <v>16.681</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2983,7 +2952,7 @@
         <v>10.012</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4484,14 +4453,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:R201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4531,8 +4500,11 @@
       <c r="Q1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4578,8 +4550,12 @@
         <f t="array" ref="Q2">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,O2+J2,J2)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" cm="1">
+        <f t="array" ref="R2">_xlfn.SEQUENCE(INT((P2-O2)/J2)+1,1,0,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4587,7 +4563,7 @@
         <v>16.247</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4595,7 +4571,7 @@
         <v>4.406</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4603,7 +4579,7 @@
         <v>4.481</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4611,7 +4587,7 @@
         <v>3.186</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4619,7 +4595,7 @@
         <v>3.324</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4627,7 +4603,7 @@
         <v>5.633</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4635,7 +4611,7 @@
         <v>7.402</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4643,7 +4619,7 @@
         <v>9.021000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4651,7 +4627,7 @@
         <v>4.887</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4659,7 +4635,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4667,7 +4643,7 @@
         <v>7.199</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4675,7 +4651,7 @@
         <v>6.894</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4683,7 +4659,7 @@
         <v>5.263</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>15</v>
       </c>

--- a/100040000/output.xlsx
+++ b/100040000/output.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505" codeName="{37E998C4-C9E5-D4B9-71C8-EB1FF731991C}"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
@@ -1039,6 +1039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2746,6 +2747,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:R201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4453,6 +4455,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:R201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
